--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,9 +1029,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1143,9 +1140,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1489,9 +1483,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2105,14 +2096,7 @@
       <c r="O29" t="n">
         <v>39</v>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2285,14 +2269,7 @@
       <c r="O32" t="n">
         <v>54</v>
       </c>
-      <c r="P32" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
@@ -2354,14 +2331,7 @@
       <c r="O33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
@@ -2654,14 +2624,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2718,9 +2681,6 @@
       </c>
       <c r="O39" t="n">
         <v>60</v>
-      </c>
-      <c r="P39" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2838,14 +2798,7 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2961,14 +2914,7 @@
       <c r="O43" t="n">
         <v>56</v>
       </c>
-      <c r="P43" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3084,9 +3030,6 @@
       <c r="O45" t="n">
         <v>43</v>
       </c>
-      <c r="P45" t="n">
-        <v>22</v>
-      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3145,14 +3088,7 @@
       <c r="O46" t="n">
         <v>54</v>
       </c>
-      <c r="P46" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3678,9 +3614,6 @@
       <c r="O55" t="n">
         <v>60</v>
       </c>
-      <c r="P55" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3859,9 +3792,6 @@
       <c r="O58" t="n">
         <v>49</v>
       </c>
-      <c r="P58" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3920,11 +3850,7 @@
       <c r="O59" t="n">
         <v>48</v>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
     </row>
@@ -3982,14 +3908,7 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4047,11 +3966,7 @@
       <c r="O61" t="n">
         <v>48</v>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4167,9 +4082,6 @@
       <c r="O63" t="n">
         <v>60</v>
       </c>
-      <c r="P63" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
@@ -4281,9 +4193,6 @@
       <c r="O65" t="n">
         <v>80</v>
       </c>
-      <c r="P65" t="n">
-        <v>20</v>
-      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
@@ -4346,9 +4255,6 @@
       <c r="O66" t="n">
         <v>60</v>
       </c>
-      <c r="P66" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
@@ -4589,14 +4495,7 @@
       <c r="O70" t="n">
         <v>45</v>
       </c>
-      <c r="P70" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4654,14 +4553,7 @@
       <c r="O71" t="n">
         <v>54</v>
       </c>
-      <c r="P71" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4835,9 +4727,6 @@
       <c r="O74" t="n">
         <v>43</v>
       </c>
-      <c r="P74" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
@@ -4954,9 +4843,6 @@
       <c r="O76" t="n">
         <v>45</v>
       </c>
-      <c r="P76" t="n">
-        <v>17</v>
-      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
@@ -5015,11 +4901,7 @@
       <c r="O77" t="n">
         <v>48</v>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
@@ -5081,14 +4963,7 @@
       <c r="O78" t="n">
         <v>47</v>
       </c>
-      <c r="P78" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
     </row>
@@ -5204,14 +5079,7 @@
       <c r="O80" t="n">
         <v>54</v>
       </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
     </row>
@@ -5563,14 +5431,7 @@
       <c r="O86" t="n">
         <v>54</v>
       </c>
-      <c r="P86" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
@@ -5748,14 +5609,7 @@
       <c r="O89" t="n">
         <v>46</v>
       </c>
-      <c r="P89" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
@@ -5879,14 +5733,7 @@
       <c r="O91" t="n">
         <v>44</v>
       </c>
-      <c r="P91" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr"/>
     </row>
@@ -5944,14 +5791,7 @@
       <c r="O92" t="n">
         <v>37</v>
       </c>
-      <c r="P92" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr"/>
     </row>
@@ -6124,9 +5964,6 @@
       </c>
       <c r="O95" t="n">
         <v>43</v>
-      </c>
-      <c r="P95" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -6847,14 +6684,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6916,14 +6746,7 @@
       <c r="O3" t="n">
         <v>54</v>
       </c>
-      <c r="P3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6985,14 +6808,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -7235,9 +7051,6 @@
       <c r="O8" t="n">
         <v>80</v>
       </c>
-      <c r="P8" t="n">
-        <v>20</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -7300,9 +7113,6 @@
       <c r="O9" t="n">
         <v>60</v>
       </c>
-      <c r="P9" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
@@ -7427,11 +7237,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -7555,14 +7361,7 @@
       <c r="O13" t="n">
         <v>54</v>
       </c>
-      <c r="P13" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -7624,14 +7423,7 @@
       <c r="O14" t="n">
         <v>46</v>
       </c>
-      <c r="P14" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
@@ -7754,9 +7546,6 @@
       </c>
       <c r="O16" t="n">
         <v>43</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1143,9 +1140,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1373,9 +1367,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -2216,14 +2207,7 @@
       <c r="O31" t="n">
         <v>54</v>
       </c>
-      <c r="P31" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2281,14 +2265,7 @@
       <c r="O32" t="n">
         <v>39</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
@@ -2461,14 +2438,7 @@
       <c r="O35" t="n">
         <v>45</v>
       </c>
-      <c r="P35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
@@ -2530,14 +2500,7 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2653,14 +2616,7 @@
       <c r="O38" t="n">
         <v>56</v>
       </c>
-      <c r="P38" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2776,14 +2732,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2957,9 +2906,6 @@
       <c r="O43" t="n">
         <v>60</v>
       </c>
-      <c r="P43" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3076,14 +3022,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3435,9 +3374,6 @@
       <c r="O51" t="n">
         <v>43</v>
       </c>
-      <c r="P51" t="n">
-        <v>22</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3496,14 +3432,7 @@
       <c r="O52" t="n">
         <v>54</v>
       </c>
-      <c r="P52" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
     </row>
@@ -3619,11 +3548,7 @@
       <c r="O54" t="n">
         <v>48</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
@@ -3743,11 +3668,7 @@
       <c r="O56" t="n">
         <v>48</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3799,9 +3720,6 @@
       </c>
       <c r="O57" t="n">
         <v>80</v>
-      </c>
-      <c r="P57" t="n">
-        <v>20</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3865,11 +3783,7 @@
       <c r="O58" t="n">
         <v>48</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -3985,9 +3899,6 @@
       <c r="O60" t="n">
         <v>60</v>
       </c>
-      <c r="P60" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
@@ -4170,14 +4081,7 @@
       <c r="O63" t="n">
         <v>45</v>
       </c>
-      <c r="P63" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4351,9 +4255,6 @@
       <c r="O66" t="n">
         <v>60</v>
       </c>
-      <c r="P66" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4412,14 +4313,7 @@
       <c r="O67" t="n">
         <v>54</v>
       </c>
-      <c r="P67" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4476,9 +4370,6 @@
       </c>
       <c r="O68" t="n">
         <v>60</v>
-      </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4596,9 +4487,6 @@
       <c r="O70" t="n">
         <v>45</v>
       </c>
-      <c r="P70" t="n">
-        <v>17</v>
-      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4835,14 +4723,7 @@
       <c r="O74" t="n">
         <v>54</v>
       </c>
-      <c r="P74" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
     </row>
@@ -5078,14 +4959,7 @@
       <c r="O78" t="n">
         <v>54</v>
       </c>
-      <c r="P78" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
@@ -5209,9 +5083,6 @@
       <c r="O80" t="n">
         <v>43</v>
       </c>
-      <c r="P80" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
@@ -5328,14 +5199,7 @@
       <c r="O82" t="n">
         <v>47</v>
       </c>
-      <c r="P82" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
     </row>
@@ -5451,14 +5315,7 @@
       <c r="O84" t="n">
         <v>46</v>
       </c>
-      <c r="P84" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
@@ -5636,9 +5493,6 @@
       <c r="O87" t="n">
         <v>44</v>
       </c>
-      <c r="P87" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
@@ -5759,14 +5613,7 @@
       <c r="O89" t="n">
         <v>44</v>
       </c>
-      <c r="P89" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
     </row>
@@ -5824,14 +5671,7 @@
       <c r="O90" t="n">
         <v>37</v>
       </c>
-      <c r="P90" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
     </row>
@@ -6546,14 +6386,7 @@
       <c r="O2" t="n">
         <v>39</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6615,14 +6448,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6746,11 +6572,7 @@
       <c r="O5" t="n">
         <v>48</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -6806,9 +6628,6 @@
       </c>
       <c r="O6" t="n">
         <v>80</v>
-      </c>
-      <c r="P6" t="n">
-        <v>20</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -6872,9 +6691,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -7123,14 +6939,7 @@
       <c r="O11" t="n">
         <v>54</v>
       </c>
-      <c r="P11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -7254,14 +7063,7 @@
       <c r="O13" t="n">
         <v>46</v>
       </c>
-      <c r="P13" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,9 +971,6 @@
       <c r="O9" t="n">
         <v>55</v>
       </c>
-      <c r="P9" t="n">
-        <v>22</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1143,9 +1140,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1547,9 +1541,6 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="P19" t="n">
-        <v>22</v>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2211,14 +2202,7 @@
       <c r="O31" t="n">
         <v>54</v>
       </c>
-      <c r="P31" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2338,14 +2322,7 @@
       <c r="O33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
@@ -2407,14 +2384,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2588,14 +2558,7 @@
       <c r="O37" t="n">
         <v>54</v>
       </c>
-      <c r="P37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2653,14 +2616,7 @@
       <c r="O38" t="n">
         <v>56</v>
       </c>
-      <c r="P38" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2776,14 +2732,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2957,9 +2906,6 @@
       <c r="O43" t="n">
         <v>60</v>
       </c>
-      <c r="P43" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3134,14 +3080,7 @@
       <c r="O46" t="n">
         <v>54</v>
       </c>
-      <c r="P46" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3547,9 +3486,6 @@
       <c r="O53" t="n">
         <v>43</v>
       </c>
-      <c r="P53" t="n">
-        <v>22</v>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3608,9 +3544,6 @@
       <c r="O54" t="n">
         <v>43</v>
       </c>
-      <c r="P54" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3669,14 +3602,7 @@
       <c r="O55" t="n">
         <v>45</v>
       </c>
-      <c r="P55" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3734,11 +3660,7 @@
       <c r="O56" t="n">
         <v>48</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
@@ -3858,11 +3780,7 @@
       <c r="O58" t="n">
         <v>48</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -3914,9 +3832,6 @@
       </c>
       <c r="O59" t="n">
         <v>80</v>
-      </c>
-      <c r="P59" t="n">
-        <v>20</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -4038,11 +3953,7 @@
       <c r="O61" t="n">
         <v>48</v>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4099,9 +4010,6 @@
       </c>
       <c r="O62" t="n">
         <v>60</v>
-      </c>
-      <c r="P62" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -4343,9 +4251,6 @@
       <c r="O66" t="n">
         <v>60</v>
       </c>
-      <c r="P66" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4404,14 +4309,7 @@
       <c r="O67" t="n">
         <v>54</v>
       </c>
-      <c r="P67" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4468,9 +4366,6 @@
       </c>
       <c r="O68" t="n">
         <v>60</v>
-      </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4530,14 +4425,7 @@
       <c r="O69" t="n">
         <v>54</v>
       </c>
-      <c r="P69" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
     </row>
@@ -4594,9 +4482,6 @@
       </c>
       <c r="O70" t="n">
         <v>45</v>
-      </c>
-      <c r="P70" t="n">
-        <v>17</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -5190,14 +5075,7 @@
       <c r="O80" t="n">
         <v>44</v>
       </c>
-      <c r="P80" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
     </row>
@@ -5254,9 +5132,6 @@
       </c>
       <c r="O81" t="n">
         <v>45</v>
-      </c>
-      <c r="P81" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -5316,14 +5191,7 @@
       <c r="O82" t="n">
         <v>54</v>
       </c>
-      <c r="P82" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
@@ -5443,14 +5311,7 @@
       <c r="O84" t="n">
         <v>47</v>
       </c>
-      <c r="P84" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
     </row>
@@ -5508,14 +5369,7 @@
       <c r="O85" t="n">
         <v>46</v>
       </c>
-      <c r="P85" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
@@ -5759,14 +5613,7 @@
       <c r="O89" t="n">
         <v>37</v>
       </c>
-      <c r="P89" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
     </row>
@@ -6423,14 +6270,7 @@
       <c r="O2" t="n">
         <v>54</v>
       </c>
-      <c r="P2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6492,14 +6332,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6561,11 +6394,7 @@
       <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6621,9 +6450,6 @@
       </c>
       <c r="O5" t="n">
         <v>80</v>
-      </c>
-      <c r="P5" t="n">
-        <v>20</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6687,9 +6513,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -7000,14 +6823,7 @@
       <c r="O11" t="n">
         <v>54</v>
       </c>
-      <c r="P11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -7069,14 +6885,7 @@
       <c r="O12" t="n">
         <v>46</v>
       </c>
-      <c r="P12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,9 +1029,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1143,9 +1140,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1489,9 +1483,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2158,14 +2149,7 @@
       <c r="O30" t="n">
         <v>54</v>
       </c>
-      <c r="P30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2334,14 +2318,7 @@
       <c r="O33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
@@ -2403,14 +2380,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2468,14 +2438,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2649,14 +2612,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2714,14 +2670,7 @@
       <c r="O39" t="n">
         <v>56</v>
       </c>
-      <c r="P39" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -3011,14 +2960,7 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3308,9 +3250,6 @@
       <c r="O49" t="n">
         <v>60</v>
       </c>
-      <c r="P49" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3427,9 +3366,6 @@
       <c r="O51" t="n">
         <v>43</v>
       </c>
-      <c r="P51" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3488,14 +3424,7 @@
       <c r="O52" t="n">
         <v>45</v>
       </c>
-      <c r="P52" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
     </row>
@@ -3553,14 +3482,7 @@
       <c r="O53" t="n">
         <v>54</v>
       </c>
-      <c r="P53" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3676,11 +3598,7 @@
       <c r="O55" t="n">
         <v>48</v>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3738,11 +3656,7 @@
       <c r="O56" t="n">
         <v>48</v>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
@@ -3920,9 +3834,6 @@
       <c r="O59" t="n">
         <v>43</v>
       </c>
-      <c r="P59" t="n">
-        <v>22</v>
-      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
@@ -4034,9 +3945,6 @@
       <c r="O61" t="n">
         <v>80</v>
       </c>
-      <c r="P61" t="n">
-        <v>20</v>
-      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
@@ -4157,11 +4065,7 @@
       <c r="O63" t="n">
         <v>48</v>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4335,9 +4239,6 @@
       <c r="O66" t="n">
         <v>60</v>
       </c>
-      <c r="P66" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
@@ -4462,9 +4363,6 @@
       <c r="O68" t="n">
         <v>60</v>
       </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -4585,9 +4483,6 @@
       <c r="O70" t="n">
         <v>45</v>
       </c>
-      <c r="P70" t="n">
-        <v>17</v>
-      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4704,9 +4599,6 @@
       <c r="O72" t="n">
         <v>60</v>
       </c>
-      <c r="P72" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
@@ -4765,14 +4657,7 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="P73" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
     </row>
@@ -5066,9 +4951,6 @@
       <c r="O78" t="n">
         <v>46</v>
       </c>
-      <c r="P78" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -5185,14 +5067,7 @@
       <c r="O80" t="n">
         <v>54</v>
       </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
@@ -5254,14 +5129,7 @@
       <c r="O81" t="n">
         <v>46</v>
       </c>
-      <c r="P81" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
@@ -5385,14 +5253,7 @@
       <c r="O83" t="n">
         <v>47</v>
       </c>
-      <c r="P83" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
     </row>
@@ -5450,14 +5311,7 @@
       <c r="O84" t="n">
         <v>44</v>
       </c>
-      <c r="P84" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
     </row>
@@ -5514,9 +5368,6 @@
       </c>
       <c r="O85" t="n">
         <v>44</v>
-      </c>
-      <c r="P85" t="n">
-        <v>13.3</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5576,14 +5427,7 @@
       <c r="O86" t="n">
         <v>54</v>
       </c>
-      <c r="P86" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr"/>
     </row>
@@ -5815,14 +5659,7 @@
       <c r="O90" t="n">
         <v>37</v>
       </c>
-      <c r="P90" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
     </row>
@@ -6425,14 +6262,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6494,11 +6324,7 @@
       <c r="O3" t="n">
         <v>48</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6554,9 +6380,6 @@
       </c>
       <c r="O4" t="n">
         <v>80</v>
-      </c>
-      <c r="P4" t="n">
-        <v>20</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -6620,9 +6443,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6871,14 +6691,7 @@
       <c r="O9" t="n">
         <v>54</v>
       </c>
-      <c r="P9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6940,14 +6753,7 @@
       <c r="O10" t="n">
         <v>46</v>
       </c>
-      <c r="P10" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,9 +1029,6 @@
       <c r="O10" t="n">
         <v>55</v>
       </c>
-      <c r="P10" t="n">
-        <v>22</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
@@ -1143,9 +1140,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1489,9 +1483,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2269,14 +2260,7 @@
       <c r="O32" t="n">
         <v>54</v>
       </c>
-      <c r="P32" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2334,14 +2318,7 @@
       <c r="O33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
@@ -2519,14 +2496,7 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2584,14 +2554,7 @@
       <c r="O37" t="n">
         <v>56</v>
       </c>
-      <c r="P37" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2823,9 +2786,6 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
-      <c r="P41" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2884,14 +2844,7 @@
       <c r="O42" t="n">
         <v>54</v>
       </c>
-      <c r="P42" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -2949,14 +2902,7 @@
       <c r="O43" t="n">
         <v>45</v>
       </c>
-      <c r="P43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3014,11 +2960,7 @@
       <c r="O44" t="n">
         <v>48</v>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3075,9 +3017,6 @@
       </c>
       <c r="O45" t="n">
         <v>43</v>
-      </c>
-      <c r="P45" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3195,9 +3134,6 @@
       <c r="O47" t="n">
         <v>60</v>
       </c>
-      <c r="P47" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
@@ -3260,14 +3196,7 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3324,9 +3253,6 @@
       </c>
       <c r="O49" t="n">
         <v>43</v>
-      </c>
-      <c r="P49" t="n">
-        <v>22</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3386,14 +3312,7 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3562,9 +3481,6 @@
       <c r="O53" t="n">
         <v>80</v>
       </c>
-      <c r="P53" t="n">
-        <v>20</v>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
@@ -3689,9 +3605,6 @@
       <c r="O55" t="n">
         <v>60</v>
       </c>
-      <c r="P55" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3750,14 +3663,7 @@
       <c r="O56" t="n">
         <v>54</v>
       </c>
-      <c r="P56" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3814,9 +3720,6 @@
       </c>
       <c r="O57" t="n">
         <v>45</v>
-      </c>
-      <c r="P57" t="n">
-        <v>17</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3876,11 +3779,7 @@
       <c r="O58" t="n">
         <v>48</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
@@ -4120,9 +4019,6 @@
       <c r="O62" t="n">
         <v>60</v>
       </c>
-      <c r="P62" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4239,11 +4135,7 @@
       <c r="O64" t="n">
         <v>48</v>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
     </row>
@@ -4417,9 +4309,6 @@
       <c r="O67" t="n">
         <v>46</v>
       </c>
-      <c r="P67" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4714,14 +4603,7 @@
       <c r="O72" t="n">
         <v>47</v>
       </c>
-      <c r="P72" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -4779,14 +4661,7 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="P73" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
@@ -4906,9 +4781,6 @@
       <c r="O75" t="n">
         <v>44</v>
       </c>
-      <c r="P75" t="n">
-        <v>13.3</v>
-      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
@@ -5025,14 +4897,7 @@
       <c r="O77" t="n">
         <v>54</v>
       </c>
-      <c r="P77" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5330,14 +5195,7 @@
       <c r="O82" t="n">
         <v>46</v>
       </c>
-      <c r="P82" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
@@ -5459,7 +5317,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 60 Day Reorder Time</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
@@ -5643,12 +5501,9 @@
       <c r="O87" t="n">
         <v>44</v>
       </c>
-      <c r="P87" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -6071,14 +5926,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6139,9 +5987,6 @@
       </c>
       <c r="O3" t="n">
         <v>60</v>
-      </c>
-      <c r="P3" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -6200,9 +6045,6 @@
       <c r="O4" t="n">
         <v>80</v>
       </c>
-      <c r="P4" t="n">
-        <v>20</v>
-      </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
@@ -6327,11 +6169,7 @@
       <c r="O6" t="n">
         <v>48</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
@@ -6517,14 +6355,7 @@
       <c r="O9" t="n">
         <v>54</v>
       </c>
-      <c r="P9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6710,14 +6541,7 @@
       <c r="O12" t="n">
         <v>46</v>
       </c>
-      <c r="P12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine 100cs Buy</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6903,12 +6727,9 @@
       <c r="O15" t="n">
         <v>44</v>
       </c>
-      <c r="P15" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1600,9 +1594,6 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
-      <c r="P20" t="n">
-        <v>22</v>
-      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2269,14 +2260,7 @@
       <c r="O32" t="n">
         <v>54</v>
       </c>
-      <c r="P32" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2334,14 +2318,7 @@
       <c r="O33" t="n">
         <v>56</v>
       </c>
-      <c r="P33" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2399,14 +2376,7 @@
       <c r="O34" t="n">
         <v>45</v>
       </c>
-      <c r="P34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
@@ -2468,14 +2438,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2707,14 +2670,7 @@
       <c r="O39" t="n">
         <v>54</v>
       </c>
-      <c r="P39" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2888,14 +2844,7 @@
       <c r="O42" t="n">
         <v>54</v>
       </c>
-      <c r="P42" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -2952,9 +2901,6 @@
       </c>
       <c r="O43" t="n">
         <v>43</v>
-      </c>
-      <c r="P43" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3014,14 +2960,7 @@
       <c r="O44" t="n">
         <v>45</v>
       </c>
-      <c r="P44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3083,14 +3022,7 @@
       <c r="O45" t="n">
         <v>47</v>
       </c>
-      <c r="P45" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3206,9 +3138,6 @@
       <c r="O47" t="n">
         <v>45</v>
       </c>
-      <c r="P47" t="n">
-        <v>17</v>
-      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -3267,9 +3196,6 @@
       <c r="O48" t="n">
         <v>42</v>
       </c>
-      <c r="P48" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3328,14 +3254,7 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="P49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3393,14 +3312,7 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3458,14 +3370,7 @@
       <c r="O51" t="n">
         <v>54</v>
       </c>
-      <c r="P51" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
     </row>
@@ -3639,11 +3544,7 @@
       <c r="O54" t="n">
         <v>48</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
@@ -3878,9 +3779,6 @@
       <c r="O58" t="n">
         <v>80</v>
       </c>
-      <c r="P58" t="n">
-        <v>20</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
@@ -4001,9 +3899,6 @@
       <c r="O60" t="n">
         <v>60</v>
       </c>
-      <c r="P60" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4062,9 +3957,6 @@
       <c r="O61" t="n">
         <v>60</v>
       </c>
-      <c r="P61" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
@@ -4127,11 +4019,7 @@
       <c r="O62" t="n">
         <v>48</v>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
@@ -4491,14 +4379,7 @@
       <c r="O68" t="n">
         <v>44</v>
       </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4555,9 +4436,6 @@
       </c>
       <c r="O69" t="n">
         <v>60</v>
-      </c>
-      <c r="P69" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4795,9 +4673,6 @@
       <c r="O73" t="n">
         <v>60</v>
       </c>
-      <c r="P73" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -4856,11 +4731,7 @@
       <c r="O74" t="n">
         <v>48</v>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
@@ -4980,14 +4851,7 @@
       <c r="O76" t="n">
         <v>54</v>
       </c>
-      <c r="P76" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5103,9 +4967,6 @@
       <c r="O78" t="n">
         <v>39</v>
       </c>
-      <c r="P78" t="n">
-        <v>13.3</v>
-      </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
@@ -5164,11 +5025,7 @@
       <c r="O79" t="n">
         <v>48</v>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
@@ -5348,7 +5205,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 60 Day Reorder Time</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
@@ -5415,12 +5272,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
+          <t>Bent Paddle Puff Party Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>643459380028</t>
+          <t>858106004268</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5430,59 +5287,63 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Bent Paddle Brewing Co</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>371</v>
+        <v>45</v>
       </c>
       <c r="F84" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="G84" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="H84" t="n">
-        <v>38.8</v>
+        <v>18.5</v>
       </c>
       <c r="I84" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J84" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K84" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84" t="n">
-        <v>9.75</v>
+        <v>22.71</v>
       </c>
       <c r="N84" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="O84" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q84" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Seasonal - last year ~18/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>615867915949</t>
+          <t>643459380028</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5492,66 +5353,59 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>56 Brewing</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>161</v>
+        <v>371</v>
       </c>
       <c r="F85" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="H85" t="n">
-        <v>16.2</v>
+        <v>38.8</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K85" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" t="n">
-        <v>7.04</v>
+        <v>9.75</v>
       </c>
       <c r="N85" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="O85" t="n">
-        <v>44</v>
-      </c>
-      <c r="P85" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gigli Mango Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>643459379541</t>
+          <t>615867915949</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5561,43 +5415,47 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>56 Brewing</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F86" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H86" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="I86" t="n">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="K86" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>9.77</v>
+        <v>7.04</v>
       </c>
       <c r="N86" t="n">
-        <v>704</v>
+        <v>42</v>
       </c>
       <c r="O86" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
@@ -5608,12 +5466,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Gigli Mango Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>643459379541</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5627,55 +5485,55 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>337</v>
+        <v>146</v>
       </c>
       <c r="F87" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="G87" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>20.5</v>
+        <v>12.2</v>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="J87" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="K87" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M87" t="n">
-        <v>8.67</v>
+        <v>9.77</v>
       </c>
       <c r="N87" t="n">
-        <v>52</v>
+        <v>704</v>
       </c>
       <c r="O87" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>198168611401</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5689,41 +5547,103 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>131</v>
+        <v>337</v>
       </c>
       <c r="F88" t="n">
-        <v>16.5</v>
+        <v>11.6</v>
       </c>
       <c r="G88" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" t="n">
         <v>5</v>
       </c>
-      <c r="H88" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="I88" t="n">
-        <v>150</v>
-      </c>
-      <c r="J88" t="n">
-        <v>97</v>
-      </c>
       <c r="K88" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="L88" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>9.779999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="N88" t="n">
-        <v>528</v>
+        <v>52</v>
       </c>
       <c r="O88" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
+        <is>
+          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>198168611401</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>131</v>
+      </c>
+      <c r="F89" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>150</v>
+      </c>
+      <c r="J89" t="n">
+        <v>97</v>
+      </c>
+      <c r="K89" t="n">
+        <v>54</v>
+      </c>
+      <c r="L89" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="N89" t="n">
+        <v>528</v>
+      </c>
+      <c r="O89" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
         <is>
           <t>Overstocked (16 wks on hand) - confirm before buying more; Seasonal - last year ~14/wk vs 8 now, buy ahead?</t>
         </is>
@@ -5740,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5894,14 +5814,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5963,14 +5876,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6032,11 +5938,7 @@
       <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6155,9 +6057,6 @@
       <c r="O6" t="n">
         <v>80</v>
       </c>
-      <c r="P6" t="n">
-        <v>20</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6220,9 +6119,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -6285,11 +6181,7 @@
       <c r="O8" t="n">
         <v>48</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -6537,11 +6429,7 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6603,11 +6491,7 @@
       <c r="O13" t="n">
         <v>48</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -6618,12 +6502,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
+          <t>Bent Paddle Puff Party Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>643459380028</t>
+          <t>858106004268</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6633,59 +6517,63 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>Bent Paddle Brewing Co</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>371</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="H14" t="n">
-        <v>38.8</v>
+        <v>18.5</v>
       </c>
       <c r="I14" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>9.75</v>
+        <v>22.71</v>
       </c>
       <c r="N14" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="O14" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Seasonal - last year ~18/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
+          <t>Gigli Blood Orange Margarita 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>615867915949</t>
+          <t>643459380028</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6695,66 +6583,59 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56 Brewing</t>
+          <t>Gigli MN LLC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>161</v>
+        <v>371</v>
       </c>
       <c r="F15" t="n">
-        <v>10.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="H15" t="n">
-        <v>16.2</v>
+        <v>38.8</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>7.04</v>
+        <v>9.75</v>
       </c>
       <c r="N15" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="O15" t="n">
-        <v>44</v>
-      </c>
-      <c r="P15" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gigli Mango Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Acre Ginger Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>643459379541</t>
+          <t>615867915949</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6764,43 +6645,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gigli MN LLC</t>
+          <t>56 Brewing</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F16" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>12.2</v>
+        <v>16.2</v>
       </c>
       <c r="I16" t="n">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="K16" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>9.77</v>
+        <v>7.04</v>
       </c>
       <c r="N16" t="n">
-        <v>704</v>
+        <v>42</v>
       </c>
       <c r="O16" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
@@ -6811,12 +6696,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
+          <t>Gigli Mango Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>643459379909</t>
+          <t>643459379541</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6830,55 +6715,55 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>337</v>
+        <v>146</v>
       </c>
       <c r="F17" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="G17" t="n">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>20.5</v>
+        <v>12.2</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>8.67</v>
+        <v>9.77</v>
       </c>
       <c r="N17" t="n">
-        <v>52</v>
+        <v>704</v>
       </c>
       <c r="O17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Gigli Variety 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>198168611401</t>
+          <t>643459379909</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6892,41 +6777,103 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>131</v>
+        <v>337</v>
       </c>
       <c r="F18" t="n">
-        <v>16.5</v>
+        <v>11.6</v>
       </c>
       <c r="G18" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
         <v>5</v>
       </c>
-      <c r="H18" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>150</v>
-      </c>
-      <c r="J18" t="n">
-        <v>97</v>
-      </c>
       <c r="K18" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>9.779999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="N18" t="n">
-        <v>528</v>
+        <v>52</v>
       </c>
       <c r="O18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
+        <is>
+          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Gigli Iced Tea Lemonade 10mg THC 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>198168611401</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Gigli MN LLC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>131</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>150</v>
+      </c>
+      <c r="J19" t="n">
+        <v>97</v>
+      </c>
+      <c r="K19" t="n">
+        <v>54</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="N19" t="n">
+        <v>528</v>
+      </c>
+      <c r="O19" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Overstocked (16 wks on hand) - confirm before buying more; Seasonal - last year ~14/wk vs 8 now, buy ahead?</t>
         </is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1658,9 +1652,6 @@
       <c r="O21" t="n">
         <v>55</v>
       </c>
-      <c r="P21" t="n">
-        <v>22</v>
-      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -2327,14 +2318,7 @@
       <c r="O33" t="n">
         <v>54</v>
       </c>
-      <c r="P33" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2392,14 +2376,7 @@
       <c r="O34" t="n">
         <v>56</v>
       </c>
-      <c r="P34" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2457,14 +2434,7 @@
       <c r="O35" t="n">
         <v>45</v>
       </c>
-      <c r="P35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
@@ -2526,14 +2496,7 @@
       <c r="O36" t="n">
         <v>45</v>
       </c>
-      <c r="P36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
@@ -2595,14 +2558,7 @@
       <c r="O37" t="n">
         <v>47</v>
       </c>
-      <c r="P37" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2834,14 +2790,7 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2898,9 +2847,6 @@
       </c>
       <c r="O42" t="n">
         <v>45</v>
-      </c>
-      <c r="P42" t="n">
-        <v>17</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2960,9 +2906,6 @@
       <c r="O43" t="n">
         <v>42</v>
       </c>
-      <c r="P43" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3137,9 +3080,6 @@
       <c r="O46" t="n">
         <v>43</v>
       </c>
-      <c r="P46" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3198,11 +3138,7 @@
       <c r="O47" t="n">
         <v>48</v>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3438,9 +3374,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3610,9 +3543,6 @@
       <c r="O54" t="n">
         <v>80</v>
       </c>
-      <c r="P54" t="n">
-        <v>20</v>
-      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
@@ -3675,14 +3605,7 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="P55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3918,9 +3841,6 @@
       <c r="O59" t="n">
         <v>60</v>
       </c>
-      <c r="P59" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4049,14 +3969,7 @@
       <c r="O61" t="n">
         <v>54</v>
       </c>
-      <c r="P61" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4114,11 +4027,7 @@
       <c r="O62" t="n">
         <v>48</v>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
@@ -4416,14 +4325,7 @@
       <c r="O67" t="n">
         <v>44</v>
       </c>
-      <c r="P67" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4480,9 +4382,6 @@
       </c>
       <c r="O68" t="n">
         <v>60</v>
-      </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4604,14 +4503,7 @@
       <c r="O70" t="n">
         <v>54</v>
       </c>
-      <c r="P70" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4668,9 +4560,6 @@
       </c>
       <c r="O71" t="n">
         <v>60</v>
-      </c>
-      <c r="P71" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4730,11 +4619,7 @@
       <c r="O72" t="n">
         <v>48</v>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
@@ -4858,11 +4743,7 @@
       <c r="O74" t="n">
         <v>48</v>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
@@ -4923,9 +4804,6 @@
       </c>
       <c r="O75" t="n">
         <v>40</v>
-      </c>
-      <c r="P75" t="n">
-        <v>13.3</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -5101,14 +4979,7 @@
       <c r="O78" t="n">
         <v>54</v>
       </c>
-      <c r="P78" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
     </row>
@@ -5224,9 +5095,6 @@
       <c r="O80" t="n">
         <v>43</v>
       </c>
-      <c r="P80" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
@@ -5289,14 +5157,7 @@
       <c r="O81" t="n">
         <v>37</v>
       </c>
-      <c r="P81" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
     </row>
@@ -5412,14 +5273,7 @@
       <c r="O83" t="n">
         <v>30</v>
       </c>
-      <c r="P83" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
@@ -5481,14 +5335,7 @@
       <c r="O84" t="n">
         <v>44</v>
       </c>
-      <c r="P84" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
@@ -5608,12 +5455,9 @@
       <c r="O86" t="n">
         <v>41</v>
       </c>
-      <c r="P86" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -6156,14 +6000,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6225,14 +6062,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6294,11 +6124,7 @@
       <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6354,9 +6180,6 @@
       </c>
       <c r="O5" t="n">
         <v>80</v>
-      </c>
-      <c r="P5" t="n">
-        <v>20</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6482,9 +6305,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6613,11 +6433,7 @@
       <c r="O9" t="n">
         <v>48</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6741,9 +6557,6 @@
       <c r="O11" t="n">
         <v>60</v>
       </c>
-      <c r="P11" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
@@ -6806,11 +6619,7 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6934,11 +6743,7 @@
       <c r="O14" t="n">
         <v>48</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
@@ -6999,9 +6804,6 @@
       </c>
       <c r="O15" t="n">
         <v>43</v>
-      </c>
-      <c r="P15" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7065,14 +6867,7 @@
       <c r="O16" t="n">
         <v>30</v>
       </c>
-      <c r="P16" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
@@ -7134,14 +6929,7 @@
       <c r="O17" t="n">
         <v>44</v>
       </c>
-      <c r="P17" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1716,9 +1710,6 @@
       <c r="O22" t="n">
         <v>55</v>
       </c>
-      <c r="P22" t="n">
-        <v>22</v>
-      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
@@ -2269,14 +2260,7 @@
       <c r="O32" t="n">
         <v>56</v>
       </c>
-      <c r="P32" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
     </row>
@@ -2392,14 +2376,7 @@
       <c r="O34" t="n">
         <v>45</v>
       </c>
-      <c r="P34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
@@ -2461,14 +2438,7 @@
       <c r="O35" t="n">
         <v>45</v>
       </c>
-      <c r="P35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
@@ -2529,9 +2499,6 @@
       </c>
       <c r="O36" t="n">
         <v>45</v>
-      </c>
-      <c r="P36" t="n">
-        <v>17</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2591,14 +2558,7 @@
       <c r="O37" t="n">
         <v>54</v>
       </c>
-      <c r="P37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2656,14 +2616,7 @@
       <c r="O38" t="n">
         <v>47</v>
       </c>
-      <c r="P38" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2779,11 +2732,7 @@
       <c r="O40" t="n">
         <v>48</v>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
@@ -2961,14 +2910,7 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="P43" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3084,9 +3026,6 @@
       <c r="O45" t="n">
         <v>60</v>
       </c>
-      <c r="P45" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -3152,9 +3091,6 @@
       </c>
       <c r="O46" t="n">
         <v>60</v>
-      </c>
-      <c r="P46" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3214,9 +3150,6 @@
       <c r="O47" t="n">
         <v>43</v>
       </c>
-      <c r="P47" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -3275,14 +3208,7 @@
       <c r="O48" t="n">
         <v>44</v>
       </c>
-      <c r="P48" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3393,9 +3319,6 @@
       <c r="O50" t="n">
         <v>80</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
@@ -3458,9 +3381,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -4049,14 +3969,7 @@
       <c r="O61" t="n">
         <v>54</v>
       </c>
-      <c r="P61" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4171,14 +4084,7 @@
       <c r="O63" t="n">
         <v>54</v>
       </c>
-      <c r="P63" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4235,9 +4141,6 @@
       </c>
       <c r="O64" t="n">
         <v>40</v>
-      </c>
-      <c r="P64" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -4355,11 +4258,7 @@
       <c r="O66" t="n">
         <v>48</v>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4537,9 +4436,6 @@
       <c r="O69" t="n">
         <v>60</v>
       </c>
-      <c r="P69" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
@@ -4602,11 +4498,7 @@
       <c r="O70" t="n">
         <v>48</v>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
@@ -4667,9 +4559,6 @@
       </c>
       <c r="O71" t="n">
         <v>39</v>
-      </c>
-      <c r="P71" t="n">
-        <v>13.3</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4787,14 +4676,7 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="P73" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
     </row>
@@ -4852,11 +4734,7 @@
       <c r="O74" t="n">
         <v>48</v>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
@@ -5038,14 +4916,7 @@
       <c r="O77" t="n">
         <v>30</v>
       </c>
-      <c r="P77" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
@@ -5106,9 +4977,6 @@
       </c>
       <c r="O78" t="n">
         <v>50</v>
-      </c>
-      <c r="P78" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -5172,14 +5040,7 @@
       <c r="O79" t="n">
         <v>37</v>
       </c>
-      <c r="P79" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5237,14 +5098,7 @@
       <c r="O80" t="n">
         <v>44</v>
       </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
@@ -5422,9 +5276,6 @@
       <c r="O83" t="n">
         <v>43</v>
       </c>
-      <c r="P83" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
@@ -5487,12 +5338,9 @@
       <c r="O84" t="n">
         <v>41</v>
       </c>
-      <c r="P84" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
@@ -6082,14 +5930,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6151,14 +5992,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6220,11 +6054,7 @@
       <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6286,9 +6116,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6349,9 +6176,6 @@
       </c>
       <c r="O6" t="n">
         <v>80</v>
-      </c>
-      <c r="P6" t="n">
-        <v>20</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -6658,9 +6482,6 @@
       <c r="O11" t="n">
         <v>60</v>
       </c>
-      <c r="P11" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
@@ -6723,11 +6544,7 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6789,11 +6606,7 @@
       <c r="O13" t="n">
         <v>48</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -6917,14 +6730,7 @@
       <c r="O15" t="n">
         <v>30</v>
       </c>
-      <c r="P15" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
@@ -6985,9 +6791,6 @@
       </c>
       <c r="O16" t="n">
         <v>50</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7051,14 +6854,7 @@
       <c r="O17" t="n">
         <v>44</v>
       </c>
-      <c r="P17" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
@@ -7119,9 +6915,6 @@
       </c>
       <c r="O18" t="n">
         <v>43</v>
-      </c>
-      <c r="P18" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1658,9 +1652,6 @@
       <c r="O21" t="n">
         <v>55</v>
       </c>
-      <c r="P21" t="n">
-        <v>22</v>
-      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
@@ -2269,14 +2260,7 @@
       <c r="O32" t="n">
         <v>45</v>
       </c>
-      <c r="P32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
@@ -2396,14 +2380,7 @@
       <c r="O34" t="n">
         <v>56</v>
       </c>
-      <c r="P34" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2461,14 +2438,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2525,9 +2495,6 @@
       </c>
       <c r="O36" t="n">
         <v>45</v>
-      </c>
-      <c r="P36" t="n">
-        <v>17</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2645,14 +2612,7 @@
       <c r="O38" t="n">
         <v>47</v>
       </c>
-      <c r="P38" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2710,14 +2670,7 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2779,14 +2732,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2844,9 +2790,6 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
-      <c r="P41" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2913,11 +2856,7 @@
       <c r="O42" t="n">
         <v>48</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -2974,9 +2913,6 @@
       </c>
       <c r="O43" t="n">
         <v>43</v>
-      </c>
-      <c r="P43" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3152,14 +3088,7 @@
       <c r="O46" t="n">
         <v>54</v>
       </c>
-      <c r="P46" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3219,7 +3148,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Quarterly buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -3461,9 +3390,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3522,11 +3448,7 @@
       <c r="O52" t="n">
         <v>48</v>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
@@ -3582,9 +3504,6 @@
       </c>
       <c r="O53" t="n">
         <v>80</v>
-      </c>
-      <c r="P53" t="n">
-        <v>20</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3644,14 +3563,7 @@
       <c r="O54" t="n">
         <v>54</v>
       </c>
-      <c r="P54" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3709,14 +3621,7 @@
       <c r="O55" t="n">
         <v>44</v>
       </c>
-      <c r="P55" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3890,9 +3795,6 @@
       <c r="O58" t="n">
         <v>60</v>
       </c>
-      <c r="P58" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3951,9 +3853,6 @@
       <c r="O59" t="n">
         <v>43</v>
       </c>
-      <c r="P59" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
@@ -4194,14 +4093,7 @@
       <c r="O63" t="n">
         <v>54</v>
       </c>
-      <c r="P63" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4375,14 +4267,7 @@
       <c r="O66" t="n">
         <v>54</v>
       </c>
-      <c r="P66" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4440,11 +4325,7 @@
       <c r="O67" t="n">
         <v>48</v>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4560,9 +4441,6 @@
       <c r="O69" t="n">
         <v>60</v>
       </c>
-      <c r="P69" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
@@ -4625,9 +4503,6 @@
       <c r="O70" t="n">
         <v>85</v>
       </c>
-      <c r="P70" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4802,9 +4677,6 @@
       <c r="O73" t="n">
         <v>47</v>
       </c>
-      <c r="P73" t="n">
-        <v>22</v>
-      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -4921,14 +4793,7 @@
       <c r="O75" t="n">
         <v>44</v>
       </c>
-      <c r="P75" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
@@ -4990,14 +4855,7 @@
       <c r="O76" t="n">
         <v>31</v>
       </c>
-      <c r="P76" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5299,9 +5157,6 @@
       <c r="O81" t="n">
         <v>37</v>
       </c>
-      <c r="P81" t="n">
-        <v>20</v>
-      </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
@@ -5360,9 +5215,6 @@
       <c r="O82" t="n">
         <v>52</v>
       </c>
-      <c r="P82" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
@@ -5425,12 +5277,9 @@
       <c r="O83" t="n">
         <v>41</v>
       </c>
-      <c r="P83" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R83" t="inlineStr"/>
@@ -5915,9 +5764,6 @@
       </c>
       <c r="O91" t="n">
         <v>65</v>
-      </c>
-      <c r="P91" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -6096,14 +5942,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6165,14 +6004,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6234,9 +6066,6 @@
       <c r="O4" t="n">
         <v>60</v>
       </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6305,7 +6134,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Quarterly buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -6431,11 +6260,7 @@
       <c r="O7" t="n">
         <v>48</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -6496,9 +6321,6 @@
       </c>
       <c r="O8" t="n">
         <v>43</v>
-      </c>
-      <c r="P8" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -6624,9 +6446,6 @@
       <c r="O10" t="n">
         <v>60</v>
       </c>
-      <c r="P10" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
@@ -6689,14 +6508,7 @@
       <c r="O11" t="n">
         <v>44</v>
       </c>
-      <c r="P11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6944,9 +6756,6 @@
       <c r="O15" t="n">
         <v>52</v>
       </c>
-      <c r="P15" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
@@ -7318,9 +7127,6 @@
       </c>
       <c r="O21" t="n">
         <v>65</v>
-      </c>
-      <c r="P21" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -7489,9 +7295,6 @@
       <c r="O2" t="n">
         <v>41</v>
       </c>
-      <c r="P2" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1542,9 +1536,6 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="P19" t="n">
-        <v>22</v>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -2327,14 +2318,7 @@
       <c r="O33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
@@ -2396,14 +2380,7 @@
       <c r="O34" t="n">
         <v>47</v>
       </c>
-      <c r="P34" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2461,14 +2438,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2584,9 +2554,6 @@
       <c r="O37" t="n">
         <v>45</v>
       </c>
-      <c r="P37" t="n">
-        <v>17</v>
-      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -2645,14 +2612,7 @@
       <c r="O38" t="n">
         <v>56</v>
       </c>
-      <c r="P38" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2710,9 +2670,6 @@
       <c r="O39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2779,14 +2736,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2844,14 +2794,7 @@
       <c r="O41" t="n">
         <v>45</v>
       </c>
-      <c r="P41" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
@@ -2971,9 +2914,6 @@
       <c r="O43" t="n">
         <v>43</v>
       </c>
-      <c r="P43" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
@@ -3090,14 +3030,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3155,11 +3088,7 @@
       <c r="O46" t="n">
         <v>48</v>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
@@ -3223,7 +3152,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Quarterly buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -3287,14 +3216,7 @@
       <c r="O48" t="n">
         <v>44</v>
       </c>
-      <c r="P48" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3351,9 +3273,6 @@
       </c>
       <c r="O49" t="n">
         <v>60</v>
-      </c>
-      <c r="P49" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3413,14 +3332,7 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3772,9 +3684,6 @@
       <c r="O56" t="n">
         <v>60</v>
       </c>
-      <c r="P56" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3833,11 +3742,7 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -3894,9 +3799,6 @@
       </c>
       <c r="O58" t="n">
         <v>43</v>
-      </c>
-      <c r="P58" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -4018,11 +3920,7 @@
       <c r="O60" t="n">
         <v>48</v>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
@@ -4142,14 +4040,7 @@
       <c r="O62" t="n">
         <v>54</v>
       </c>
-      <c r="P62" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4323,14 +4214,7 @@
       <c r="O65" t="n">
         <v>54</v>
       </c>
-      <c r="P65" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
@@ -4387,9 +4271,6 @@
       </c>
       <c r="O66" t="n">
         <v>84</v>
-      </c>
-      <c r="P66" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4507,9 +4388,6 @@
       <c r="O68" t="n">
         <v>60</v>
       </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
@@ -4572,14 +4450,7 @@
       <c r="O69" t="n">
         <v>44</v>
       </c>
-      <c r="P69" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
@@ -4815,9 +4686,6 @@
       <c r="O73" t="n">
         <v>47</v>
       </c>
-      <c r="P73" t="n">
-        <v>22</v>
-      </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
@@ -5360,9 +5228,6 @@
       <c r="O82" t="n">
         <v>37</v>
       </c>
-      <c r="P82" t="n">
-        <v>20</v>
-      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
@@ -5479,14 +5344,7 @@
       <c r="O84" t="n">
         <v>31</v>
       </c>
-      <c r="P84" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
     </row>
@@ -5602,12 +5460,9 @@
       <c r="O86" t="n">
         <v>41</v>
       </c>
-      <c r="P86" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -6034,9 +5889,6 @@
       </c>
       <c r="O93" t="n">
         <v>65</v>
-      </c>
-      <c r="P93" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6215,14 +6067,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6284,9 +6129,6 @@
       <c r="O3" t="n">
         <v>60</v>
       </c>
-      <c r="P3" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6353,14 +6195,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6422,11 +6257,7 @@
       <c r="O5" t="n">
         <v>48</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -6490,7 +6321,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Quarterly buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
@@ -6616,9 +6447,6 @@
       <c r="O8" t="n">
         <v>43</v>
       </c>
-      <c r="P8" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6681,11 +6509,7 @@
       <c r="O9" t="n">
         <v>48</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6746,9 +6570,6 @@
       </c>
       <c r="O10" t="n">
         <v>60</v>
-      </c>
-      <c r="P10" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -6812,14 +6633,7 @@
       <c r="O11" t="n">
         <v>44</v>
       </c>
-      <c r="P11" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -7500,9 +7314,6 @@
       </c>
       <c r="O22" t="n">
         <v>65</v>
-      </c>
-      <c r="P22" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -7671,9 +7482,6 @@
       <c r="O2" t="n">
         <v>41</v>
       </c>
-      <c r="P2" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1484,9 +1478,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2269,14 +2260,7 @@
       <c r="O32" t="n">
         <v>45</v>
       </c>
-      <c r="P32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
@@ -2396,14 +2380,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2519,9 +2496,6 @@
       <c r="O36" t="n">
         <v>45</v>
       </c>
-      <c r="P36" t="n">
-        <v>17</v>
-      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
@@ -2638,14 +2612,7 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="P38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
     </row>
@@ -2703,9 +2670,6 @@
       <c r="O39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2772,14 +2736,7 @@
       <c r="O40" t="n">
         <v>56</v>
       </c>
-      <c r="P40" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2837,11 +2794,7 @@
       <c r="O41" t="n">
         <v>48</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
@@ -2905,7 +2858,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Quarterly buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -2969,14 +2922,7 @@
       <c r="O43" t="n">
         <v>45</v>
       </c>
-      <c r="P43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
@@ -3096,14 +3042,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3160,9 +3099,6 @@
       </c>
       <c r="O46" t="n">
         <v>43</v>
-      </c>
-      <c r="P46" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3222,14 +3158,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3287,14 +3216,7 @@
       <c r="O48" t="n">
         <v>47</v>
       </c>
-      <c r="P48" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3588,9 +3510,6 @@
       <c r="O53" t="n">
         <v>43</v>
       </c>
-      <c r="P53" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
@@ -3653,11 +3572,7 @@
       <c r="O54" t="n">
         <v>48</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
@@ -3777,9 +3692,6 @@
       <c r="O56" t="n">
         <v>60</v>
       </c>
-      <c r="P56" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
@@ -3900,9 +3812,6 @@
       <c r="O58" t="n">
         <v>60</v>
       </c>
-      <c r="P58" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -4081,14 +3990,7 @@
       <c r="O61" t="n">
         <v>44</v>
       </c>
-      <c r="P61" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4146,14 +4048,7 @@
       <c r="O62" t="n">
         <v>54</v>
       </c>
-      <c r="P62" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4269,11 +4164,7 @@
       <c r="O64" t="n">
         <v>48</v>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
     </row>
@@ -4389,14 +4280,7 @@
       <c r="O66" t="n">
         <v>54</v>
       </c>
-      <c r="P66" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4453,9 +4337,6 @@
       </c>
       <c r="O67" t="n">
         <v>85</v>
-      </c>
-      <c r="P67" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4693,9 +4574,6 @@
       <c r="O71" t="n">
         <v>60</v>
       </c>
-      <c r="P71" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
@@ -4936,14 +4814,7 @@
       <c r="O75" t="n">
         <v>44</v>
       </c>
-      <c r="P75" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
@@ -5005,14 +4876,7 @@
       <c r="O76" t="n">
         <v>32</v>
       </c>
-      <c r="P76" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5364,9 +5228,6 @@
       <c r="O82" t="n">
         <v>37</v>
       </c>
-      <c r="P82" t="n">
-        <v>20</v>
-      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
@@ -5425,9 +5286,6 @@
       <c r="O83" t="n">
         <v>47</v>
       </c>
-      <c r="P83" t="n">
-        <v>22</v>
-      </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
@@ -5486,14 +5344,7 @@
       <c r="O84" t="n">
         <v>37</v>
       </c>
-      <c r="P84" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
     </row>
@@ -5613,12 +5464,9 @@
       <c r="O86" t="n">
         <v>41</v>
       </c>
-      <c r="P86" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Case 1</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R86" t="inlineStr"/>
@@ -6045,9 +5893,6 @@
       </c>
       <c r="O93" t="n">
         <v>65</v>
-      </c>
-      <c r="P93" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6288,14 +6133,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6357,9 +6195,6 @@
       <c r="O3" t="n">
         <v>60</v>
       </c>
-      <c r="P3" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6426,11 +6261,7 @@
       <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6494,7 +6325,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Quarterly buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -6558,14 +6389,7 @@
       <c r="O6" t="n">
         <v>45</v>
       </c>
-      <c r="P6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
@@ -6689,9 +6513,6 @@
       <c r="O8" t="n">
         <v>43</v>
       </c>
-      <c r="P8" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6754,11 +6575,7 @@
       <c r="O9" t="n">
         <v>48</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6819,9 +6636,6 @@
       </c>
       <c r="O10" t="n">
         <v>60</v>
-      </c>
-      <c r="P10" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -7009,9 +6823,6 @@
       <c r="O13" t="n">
         <v>60</v>
       </c>
-      <c r="P13" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -7136,14 +6947,7 @@
       <c r="O15" t="n">
         <v>44</v>
       </c>
-      <c r="P15" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
@@ -7638,9 +7442,6 @@
       </c>
       <c r="O23" t="n">
         <v>65</v>
-      </c>
-      <c r="P23" t="n">
-        <v>70.8</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -7871,9 +7672,6 @@
       <c r="O2" t="n">
         <v>41</v>
       </c>
-      <c r="P2" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1431,9 +1425,6 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
-      <c r="P17" t="n">
-        <v>22</v>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -2105,14 +2096,7 @@
       <c r="O29" t="n">
         <v>45</v>
       </c>
-      <c r="P29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2343,9 +2327,6 @@
       <c r="O33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
-        <v>17</v>
-      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2466,14 +2447,7 @@
       <c r="O35" t="n">
         <v>45</v>
       </c>
-      <c r="P35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
@@ -2535,14 +2509,7 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2599,9 +2566,6 @@
       </c>
       <c r="O37" t="n">
         <v>60</v>
-      </c>
-      <c r="P37" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2781,9 +2745,6 @@
       <c r="O40" t="n">
         <v>84</v>
       </c>
-      <c r="P40" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2842,11 +2803,7 @@
       <c r="O41" t="n">
         <v>48</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2904,14 +2861,7 @@
       <c r="O42" t="n">
         <v>56</v>
       </c>
-      <c r="P42" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
@@ -2972,9 +2922,6 @@
       </c>
       <c r="O43" t="n">
         <v>60</v>
-      </c>
-      <c r="P43" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3100,11 +3047,7 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
@@ -3165,9 +3108,6 @@
       </c>
       <c r="O46" t="n">
         <v>43</v>
-      </c>
-      <c r="P46" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3289,14 +3229,7 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3354,14 +3287,7 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="P49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3481,9 +3407,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3600,14 +3523,7 @@
       <c r="O53" t="n">
         <v>54</v>
       </c>
-      <c r="P53" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3665,14 +3581,7 @@
       <c r="O54" t="n">
         <v>44</v>
       </c>
-      <c r="P54" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3846,9 +3755,6 @@
       <c r="O57" t="n">
         <v>37</v>
       </c>
-      <c r="P57" t="n">
-        <v>20</v>
-      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -3907,11 +3813,7 @@
       <c r="O58" t="n">
         <v>73</v>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>60 Day Reorder Time</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -4027,14 +3929,7 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4150,9 +4045,6 @@
       <c r="O62" t="n">
         <v>43</v>
       </c>
-      <c r="P62" t="n">
-        <v>22</v>
-      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4211,14 +4103,7 @@
       <c r="O63" t="n">
         <v>54</v>
       </c>
-      <c r="P63" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4334,11 +4219,7 @@
       <c r="O65" t="n">
         <v>48</v>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
@@ -4524,14 +4405,7 @@
       <c r="O68" t="n">
         <v>43</v>
       </c>
-      <c r="P68" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
@@ -4651,9 +4525,6 @@
       <c r="O70" t="n">
         <v>60</v>
       </c>
-      <c r="P70" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
@@ -4836,11 +4707,7 @@
       <c r="O73" t="n">
         <v>73</v>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>60 Day Reorder Time</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
     </row>
@@ -5018,14 +4885,7 @@
       <c r="O76" t="n">
         <v>47</v>
       </c>
-      <c r="P76" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5141,14 +5001,7 @@
       <c r="O78" t="n">
         <v>37</v>
       </c>
-      <c r="P78" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Support with Free cs from SJ</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
     </row>
@@ -5206,14 +5059,7 @@
       <c r="O79" t="n">
         <v>32</v>
       </c>
-      <c r="P79" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5270,9 +5116,6 @@
       </c>
       <c r="O80" t="n">
         <v>38</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5522,12 +5365,9 @@
       <c r="O84" t="n">
         <v>44</v>
       </c>
-      <c r="P84" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
@@ -5888,14 +5728,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5957,14 +5790,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6025,9 +5851,6 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -6091,14 +5914,7 @@
       <c r="O5" t="n">
         <v>56</v>
       </c>
-      <c r="P5" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -6159,9 +5975,6 @@
       </c>
       <c r="O6" t="n">
         <v>60</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -6287,11 +6100,7 @@
       <c r="O8" t="n">
         <v>48</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -6352,9 +6161,6 @@
       </c>
       <c r="O9" t="n">
         <v>43</v>
-      </c>
-      <c r="P9" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -6480,11 +6286,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6670,14 +6472,7 @@
       <c r="O14" t="n">
         <v>43</v>
       </c>
-      <c r="P14" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
@@ -6738,9 +6533,6 @@
       </c>
       <c r="O15" t="n">
         <v>60</v>
-      </c>
-      <c r="P15" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7114,12 +6906,9 @@
       <c r="O21" t="n">
         <v>44</v>
       </c>
-      <c r="P21" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -7470,9 +7259,6 @@
       <c r="O2" t="n">
         <v>49</v>
       </c>
-      <c r="P2" t="n">
-        <v>21.3</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -7532,9 +7318,6 @@
       </c>
       <c r="O3" t="n">
         <v>42</v>
-      </c>
-      <c r="P3" t="n">
-        <v>16.7</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,6 +1145,9 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
+      <c r="P12" t="n">
+        <v>22</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1256,6 +1259,9 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
+      <c r="P14" t="n">
+        <v>22</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1425,6 +1431,9 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
+      <c r="P17" t="n">
+        <v>22</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -2096,7 +2105,14 @@
       <c r="O29" t="n">
         <v>45</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2447,6 +2463,9 @@
       <c r="O35" t="n">
         <v>45</v>
       </c>
+      <c r="P35" t="n">
+        <v>17</v>
+      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -2505,7 +2524,14 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2562,6 +2588,9 @@
       </c>
       <c r="O37" t="n">
         <v>60</v>
+      </c>
+      <c r="P37" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2683,7 +2712,14 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2744,6 +2780,9 @@
       </c>
       <c r="O40" t="n">
         <v>84</v>
+      </c>
+      <c r="P40" t="n">
+        <v>13.7</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2803,7 +2842,11 @@
       <c r="O41" t="n">
         <v>48</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2860,6 +2903,9 @@
       </c>
       <c r="O42" t="n">
         <v>60</v>
+      </c>
+      <c r="P42" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2985,7 +3031,11 @@
       <c r="O44" t="n">
         <v>48</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3046,6 +3096,9 @@
       </c>
       <c r="O45" t="n">
         <v>43</v>
+      </c>
+      <c r="P45" t="n">
+        <v>21.1</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3109,6 +3162,9 @@
       <c r="O46" t="n">
         <v>60</v>
       </c>
+      <c r="P46" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3225,7 +3281,14 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3345,7 +3408,14 @@
       <c r="O50" t="n">
         <v>56</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
@@ -3407,7 +3477,14 @@
       <c r="O51" t="n">
         <v>43</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
@@ -3469,7 +3546,14 @@
       <c r="O52" t="n">
         <v>54</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
     </row>
@@ -3527,7 +3611,14 @@
       <c r="O53" t="n">
         <v>44</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Blackberry Lemon (Purple)</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3643,7 +3734,14 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3759,7 +3857,11 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
@@ -3821,7 +3923,11 @@
       <c r="O58" t="n">
         <v>48</v>
       </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
     </row>
@@ -3937,7 +4043,14 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4053,7 +4166,11 @@
       <c r="O62" t="n">
         <v>73</v>
       </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>60 Day Reorder Time</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4110,6 +4227,9 @@
       </c>
       <c r="O63" t="n">
         <v>37</v>
+      </c>
+      <c r="P63" t="n">
+        <v>20</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -4169,6 +4289,9 @@
       <c r="O64" t="n">
         <v>60</v>
       </c>
+      <c r="P64" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
@@ -4231,7 +4354,14 @@
       <c r="O65" t="n">
         <v>54</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
@@ -4467,6 +4597,9 @@
       <c r="O69" t="n">
         <v>43</v>
       </c>
+      <c r="P69" t="n">
+        <v>22</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
@@ -4587,7 +4720,11 @@
       <c r="O71" t="n">
         <v>73</v>
       </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>60 Day Reorder Time</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4823,7 +4960,14 @@
       <c r="O75" t="n">
         <v>47</v>
       </c>
-      <c r="Q75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Kiwi Strawberry (Pink)</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -4881,7 +5025,11 @@
       <c r="O76" t="n">
         <v>73</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>60 Day Reorder Time</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5055,7 +5203,11 @@
       <c r="O79" t="n">
         <v>55</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5175,7 +5327,14 @@
       <c r="O81" t="n">
         <v>37</v>
       </c>
-      <c r="Q81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Support with Free cs from SJ</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
     </row>
@@ -5295,6 +5454,9 @@
       <c r="O83" t="n">
         <v>38</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -5357,9 +5519,12 @@
       <c r="O84" t="n">
         <v>40</v>
       </c>
+      <c r="P84" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Buy a pallet, get 9cs of Gummies Free to hit invoice net of $47</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
@@ -5605,9 +5770,12 @@
       <c r="O88" t="n">
         <v>44</v>
       </c>
+      <c r="P88" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R88" t="inlineStr"/>
@@ -5906,7 +6074,14 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5967,6 +6142,9 @@
       </c>
       <c r="O3" t="n">
         <v>60</v>
+      </c>
+      <c r="P3" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -6030,7 +6208,14 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6091,6 +6276,9 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6216,7 +6404,11 @@
       <c r="O7" t="n">
         <v>48</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -6277,6 +6469,9 @@
       </c>
       <c r="O8" t="n">
         <v>43</v>
+      </c>
+      <c r="P8" t="n">
+        <v>21.1</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -6402,7 +6597,14 @@
       <c r="O10" t="n">
         <v>56</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
@@ -6464,7 +6666,14 @@
       <c r="O11" t="n">
         <v>43</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6526,7 +6735,11 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6587,6 +6800,9 @@
       </c>
       <c r="O13" t="n">
         <v>60</v>
+      </c>
+      <c r="P13" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -7146,9 +7362,12 @@
       <c r="O22" t="n">
         <v>44</v>
       </c>
+      <c r="P22" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -7293,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7437,6 +7656,9 @@
       <c r="O2" t="n">
         <v>50</v>
       </c>
+      <c r="P2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -7446,72 +7668,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BLNCD Brain Boost Adaptogen 50mg THC Gummies 10pk</t>
+          <t>Brez Double 5mg THC 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>810012698481</t>
+          <t>197644309047</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Edibles</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Nothing But Hemp LLC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>36.5</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>11.69</v>
+        <v>2.83</v>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="O3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 8w)</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brez Double 5mg THC 12oz can</t>
+          <t>Brez Single 2.5mg THC 7.5oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>197644309047</t>
+          <t>197644087846</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7531,13 +7749,13 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>-27</v>
       </c>
       <c r="H4" t="n">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="I4" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -7549,25 +7767,25 @@
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="N4" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="O4" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brez Single 2.5mg THC 7.5oz can</t>
+          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>197644087846</t>
+          <t>643459379305</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7577,53 +7795,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nothing But Hemp LLC</t>
+          <t>Discontinued</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-27</v>
+        <v>32</v>
       </c>
       <c r="H5" t="n">
-        <v>40.5</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="K5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>235</v>
+      </c>
+      <c r="O5" t="n">
         <v>48</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>110</v>
-      </c>
-      <c r="O5" t="n">
-        <v>58</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gigli Citrus Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>643459379305</t>
+          <t>198168016879</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7637,34 +7855,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>161</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>7.9</v>
+        <v>13.9</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="I6" t="n">
-        <v>148</v>
+        <v>261</v>
       </c>
       <c r="J6" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>234</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>9.789999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="N6" t="n">
-        <v>235</v>
+        <v>2303</v>
       </c>
       <c r="O6" t="n">
         <v>48</v>
@@ -7674,12 +7892,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gigli Raspberry Tea 10mg THC 4pk 12oz can</t>
+          <t>Wikid Sparkling Paloma 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>198168016879</t>
+          <t>850046271113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7689,53 +7907,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Discontinued</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>13.9</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="H7" t="n">
-        <v>15.5</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>261</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>234</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>9.84</v>
+        <v>11.66</v>
       </c>
       <c r="N7" t="n">
-        <v>2303</v>
+        <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wikid Sparkling Paloma 5mg THC 4pk 12oz can</t>
+          <t>Wynk Lemonade Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>850046271113</t>
+          <t>198715683899</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7745,99 +7963,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>24</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>11.66</v>
+        <v>15.98</v>
       </c>
       <c r="N8" t="n">
-        <v>70</v>
+        <v>1310</v>
       </c>
       <c r="O8" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wynk Lemonade Variety Pack 10mg THC 12pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>198715683899</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>65</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>24</v>
-      </c>
-      <c r="I9" t="n">
-        <v>110</v>
-      </c>
-      <c r="J9" t="n">
-        <v>28</v>
-      </c>
-      <c r="K9" t="n">
-        <v>82</v>
-      </c>
-      <c r="L9" t="n">
-        <v>41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1310</v>
-      </c>
-      <c r="O9" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,6 +1145,9 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
+      <c r="P12" t="n">
+        <v>22</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1198,6 +1201,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1309,6 +1315,9 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
+      <c r="P15" t="n">
+        <v>22</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -2154,7 +2163,14 @@
       <c r="O30" t="n">
         <v>45</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2447,6 +2463,9 @@
       <c r="O35" t="n">
         <v>45</v>
       </c>
+      <c r="P35" t="n">
+        <v>17</v>
+      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -2505,7 +2524,14 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2679,7 +2705,11 @@
       <c r="O39" t="n">
         <v>48</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2736,6 +2766,9 @@
       </c>
       <c r="O40" t="n">
         <v>60</v>
+      </c>
+      <c r="P40" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2799,7 +2832,11 @@
       <c r="O41" t="n">
         <v>48</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
@@ -2861,7 +2898,14 @@
       <c r="O42" t="n">
         <v>45</v>
       </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
@@ -2922,6 +2966,9 @@
       </c>
       <c r="O43" t="n">
         <v>60</v>
+      </c>
+      <c r="P43" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2985,6 +3032,9 @@
       <c r="O44" t="n">
         <v>43</v>
       </c>
+      <c r="P44" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
@@ -3109,6 +3159,9 @@
       <c r="O46" t="n">
         <v>77</v>
       </c>
+      <c r="P46" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3225,7 +3278,14 @@
       <c r="O48" t="n">
         <v>43</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
@@ -3287,7 +3347,14 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3344,6 +3411,9 @@
       </c>
       <c r="O50" t="n">
         <v>60</v>
+      </c>
+      <c r="P50" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3465,7 +3535,14 @@
       <c r="O52" t="n">
         <v>44</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Blackberry Lemon (Purple)</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
     </row>
@@ -3523,7 +3600,14 @@
       <c r="O53" t="n">
         <v>56</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -3643,7 +3727,14 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3701,7 +3792,14 @@
       <c r="O56" t="n">
         <v>54</v>
       </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3759,7 +3857,11 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -3817,7 +3919,11 @@
       <c r="O58" t="n">
         <v>48</v>
       </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
@@ -3878,6 +3984,9 @@
       </c>
       <c r="O59" t="n">
         <v>37</v>
+      </c>
+      <c r="P59" t="n">
+        <v>20</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3937,7 +4046,14 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4235,7 +4351,11 @@
       <c r="O65" t="n">
         <v>73</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>60 Day Reorder Time</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
@@ -4351,7 +4471,11 @@
       <c r="O67" t="n">
         <v>55</v>
       </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4409,7 +4533,11 @@
       <c r="O68" t="n">
         <v>73</v>
       </c>
-      <c r="Q68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>60 Day Reorder Time</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4466,6 +4594,9 @@
       </c>
       <c r="O69" t="n">
         <v>60</v>
+      </c>
+      <c r="P69" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4529,6 +4660,9 @@
       <c r="O70" t="n">
         <v>43</v>
       </c>
+      <c r="P70" t="n">
+        <v>22</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
@@ -4587,7 +4721,14 @@
       <c r="O71" t="n">
         <v>54</v>
       </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4881,6 +5022,9 @@
       <c r="O76" t="n">
         <v>38</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4943,9 +5087,12 @@
       <c r="O77" t="n">
         <v>66</v>
       </c>
+      <c r="P77" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
         </is>
       </c>
       <c r="R77" t="inlineStr"/>
@@ -5195,9 +5342,12 @@
       <c r="O81" t="n">
         <v>44</v>
       </c>
+      <c r="P81" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
@@ -5496,7 +5646,14 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5557,6 +5714,9 @@
       </c>
       <c r="O3" t="n">
         <v>60</v>
+      </c>
+      <c r="P3" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -5620,7 +5780,11 @@
       <c r="O4" t="n">
         <v>48</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5682,7 +5846,14 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -5743,6 +5914,9 @@
       </c>
       <c r="O6" t="n">
         <v>60</v>
+      </c>
+      <c r="P6" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -5806,6 +5980,9 @@
       <c r="O7" t="n">
         <v>43</v>
       </c>
+      <c r="P7" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -5930,7 +6107,14 @@
       <c r="O9" t="n">
         <v>43</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6054,7 +6238,14 @@
       <c r="O11" t="n">
         <v>56</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6116,7 +6307,11 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6302,6 +6497,9 @@
       <c r="O15" t="n">
         <v>60</v>
       </c>
+      <c r="P15" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
@@ -6426,9 +6624,12 @@
       <c r="O17" t="n">
         <v>66</v>
       </c>
+      <c r="P17" t="n">
+        <v>22.2</v>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); $200 order qty per store</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -6678,9 +6879,12 @@
       <c r="O21" t="n">
         <v>44</v>
       </c>
+      <c r="P21" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -6969,6 +7173,9 @@
       <c r="O2" t="n">
         <v>50</v>
       </c>
+      <c r="P2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1207,9 +1207,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1263,9 +1260,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1319,9 +1313,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -2225,14 +2216,7 @@
       <c r="O31" t="n">
         <v>45</v>
       </c>
-      <c r="P31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2463,14 +2447,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2702,9 +2679,6 @@
       <c r="O39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2770,9 +2744,6 @@
       </c>
       <c r="O40" t="n">
         <v>60</v>
-      </c>
-      <c r="P40" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2898,9 +2869,6 @@
       <c r="O42" t="n">
         <v>79</v>
       </c>
-      <c r="P42" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -2959,9 +2927,6 @@
       <c r="O43" t="n">
         <v>43</v>
       </c>
-      <c r="P43" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
@@ -3024,9 +2989,6 @@
       <c r="O44" t="n">
         <v>60</v>
       </c>
-      <c r="P44" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -3085,11 +3047,7 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
@@ -3151,14 +3109,7 @@
       <c r="O46" t="n">
         <v>45</v>
       </c>
-      <c r="P46" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
@@ -3282,11 +3233,7 @@
       <c r="O48" t="n">
         <v>48</v>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3406,14 +3353,7 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3470,9 +3410,6 @@
       </c>
       <c r="O51" t="n">
         <v>43</v>
-      </c>
-      <c r="P51" t="n">
-        <v>22</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3532,9 +3469,6 @@
       <c r="O52" t="n">
         <v>37</v>
       </c>
-      <c r="P52" t="n">
-        <v>20</v>
-      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3593,11 +3527,7 @@
       <c r="O53" t="n">
         <v>55</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3655,11 +3585,7 @@
       <c r="O54" t="n">
         <v>48</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3717,14 +3643,7 @@
       <c r="O55" t="n">
         <v>54</v>
       </c>
-      <c r="P55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3781,9 +3700,6 @@
       </c>
       <c r="O56" t="n">
         <v>45</v>
-      </c>
-      <c r="P56" t="n">
-        <v>17</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3843,11 +3759,7 @@
       <c r="O57" t="n">
         <v>47</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -4078,9 +3990,6 @@
       </c>
       <c r="O61" t="n">
         <v>60</v>
-      </c>
-      <c r="P61" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -4859,14 +4768,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -4928,9 +4830,6 @@
       <c r="O4" t="n">
         <v>60</v>
       </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4996,9 +4895,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -5124,9 +5020,6 @@
       <c r="O7" t="n">
         <v>43</v>
       </c>
-      <c r="P7" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -5189,11 +5082,7 @@
       <c r="O8" t="n">
         <v>48</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -5255,14 +5144,7 @@
       <c r="O9" t="n">
         <v>45</v>
       </c>
-      <c r="P9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -5447,9 +5329,6 @@
       </c>
       <c r="O12" t="n">
         <v>60</v>
-      </c>
-      <c r="P12" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -6036,9 +5915,6 @@
       <c r="O4" t="n">
         <v>44</v>
       </c>
-      <c r="P4" t="n">
-        <v>52.7</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,6 +1145,9 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
+      <c r="P12" t="n">
+        <v>22</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1198,6 +1201,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1309,6 +1315,9 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
+      <c r="P15" t="n">
+        <v>22</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -2154,7 +2163,14 @@
       <c r="O30" t="n">
         <v>45</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2216,7 +2232,14 @@
       <c r="O31" t="n">
         <v>54</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2501,7 +2524,11 @@
       <c r="O36" t="n">
         <v>55</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2558,6 +2585,9 @@
       </c>
       <c r="O37" t="n">
         <v>60</v>
+      </c>
+      <c r="P37" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2683,7 +2713,14 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2744,6 +2781,9 @@
       </c>
       <c r="O40" t="n">
         <v>60</v>
+      </c>
+      <c r="P40" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2803,6 +2843,9 @@
       <c r="O41" t="n">
         <v>43</v>
       </c>
+      <c r="P41" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
@@ -2985,6 +3028,9 @@
       <c r="O44" t="n">
         <v>76</v>
       </c>
+      <c r="P44" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
@@ -3043,6 +3089,9 @@
       <c r="O45" t="n">
         <v>60</v>
       </c>
+      <c r="P45" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
@@ -3105,7 +3154,11 @@
       <c r="O46" t="n">
         <v>48</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3163,7 +3216,11 @@
       <c r="O47" t="n">
         <v>48</v>
       </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3287,6 +3344,9 @@
       <c r="O49" t="n">
         <v>43</v>
       </c>
+      <c r="P49" t="n">
+        <v>22</v>
+      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -3345,7 +3405,14 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3403,7 +3470,11 @@
       <c r="O51" t="n">
         <v>47</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
     </row>
@@ -3519,6 +3590,9 @@
       <c r="O53" t="n">
         <v>37</v>
       </c>
+      <c r="P53" t="n">
+        <v>20</v>
+      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3871,7 +3945,11 @@
       <c r="O59" t="n">
         <v>48</v>
       </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
@@ -4049,7 +4127,11 @@
       <c r="O62" t="n">
         <v>55</v>
       </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4165,6 +4247,9 @@
       <c r="O64" t="n">
         <v>35</v>
       </c>
+      <c r="P64" t="n">
+        <v>13.3</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4223,6 +4308,9 @@
       <c r="O65" t="n">
         <v>60</v>
       </c>
+      <c r="P65" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
@@ -4284,6 +4372,9 @@
       </c>
       <c r="O66" t="n">
         <v>34</v>
+      </c>
+      <c r="P66" t="n">
+        <v>25.7</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4822,7 +4913,14 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -4884,6 +4982,9 @@
       <c r="O3" t="n">
         <v>60</v>
       </c>
+      <c r="P3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -4950,7 +5051,14 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5011,6 +5119,9 @@
       </c>
       <c r="O5" t="n">
         <v>43</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -5136,6 +5247,9 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
+      <c r="P7" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -5198,7 +5312,11 @@
       <c r="O8" t="n">
         <v>48</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -5384,7 +5502,11 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -5445,6 +5567,9 @@
       </c>
       <c r="O12" t="n">
         <v>60</v>
+      </c>
+      <c r="P12" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -5507,6 +5632,9 @@
       </c>
       <c r="O13" t="n">
         <v>34</v>
+      </c>
+      <c r="P13" t="n">
+        <v>25.7</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -6031,6 +6159,9 @@
       <c r="O4" t="n">
         <v>44</v>
       </c>
+      <c r="P4" t="n">
+        <v>52.7</v>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1201,9 +1198,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1373,9 +1367,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -2163,14 +2154,7 @@
       <c r="O30" t="n">
         <v>45</v>
       </c>
-      <c r="P30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
@@ -2232,14 +2216,7 @@
       <c r="O31" t="n">
         <v>54</v>
       </c>
-      <c r="P31" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2413,11 +2390,7 @@
       <c r="O34" t="n">
         <v>55</v>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2591,9 +2564,6 @@
       <c r="O37" t="n">
         <v>60</v>
       </c>
-      <c r="P37" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2659,9 +2629,6 @@
       </c>
       <c r="O38" t="n">
         <v>78</v>
-      </c>
-      <c r="P38" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2721,14 +2688,7 @@
       <c r="O39" t="n">
         <v>45</v>
       </c>
-      <c r="P39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2848,9 +2808,6 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
-      <c r="P41" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
@@ -2971,14 +2928,7 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="P43" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3156,9 +3106,6 @@
       <c r="O46" t="n">
         <v>43</v>
       </c>
-      <c r="P46" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
@@ -3221,9 +3168,6 @@
       <c r="O47" t="n">
         <v>60</v>
       </c>
-      <c r="P47" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -3282,9 +3226,6 @@
       <c r="O48" t="n">
         <v>43</v>
       </c>
-      <c r="P48" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3343,11 +3284,7 @@
       <c r="O49" t="n">
         <v>48</v>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3695,9 +3632,6 @@
       <c r="O55" t="n">
         <v>37</v>
       </c>
-      <c r="P55" t="n">
-        <v>20</v>
-      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3756,9 +3690,6 @@
       <c r="O56" t="n">
         <v>43</v>
       </c>
-      <c r="P56" t="n">
-        <v>22</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3817,11 +3748,7 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
@@ -4003,14 +3930,7 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4246,9 +4166,6 @@
       <c r="O64" t="n">
         <v>34</v>
       </c>
-      <c r="P64" t="n">
-        <v>13.3</v>
-      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
@@ -4423,11 +4340,7 @@
       <c r="O67" t="n">
         <v>47</v>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4485,14 +4398,7 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="P68" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4550,14 +4456,7 @@
       <c r="O69" t="n">
         <v>39</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
@@ -4619,11 +4518,7 @@
       <c r="O70" t="n">
         <v>55</v>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4680,9 +4575,6 @@
       </c>
       <c r="O71" t="n">
         <v>34</v>
-      </c>
-      <c r="P71" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4746,9 +4638,6 @@
       <c r="O72" t="n">
         <v>60</v>
       </c>
-      <c r="P72" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
@@ -4811,11 +4700,7 @@
       <c r="O73" t="n">
         <v>48</v>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
@@ -4939,9 +4824,6 @@
       <c r="O75" t="n">
         <v>45</v>
       </c>
-      <c r="P75" t="n">
-        <v>17</v>
-      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
@@ -5000,14 +4882,7 @@
       <c r="O76" t="n">
         <v>44</v>
       </c>
-      <c r="P76" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5656,14 +5531,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5725,9 +5593,6 @@
       <c r="O3" t="n">
         <v>60</v>
       </c>
-      <c r="P3" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -5794,14 +5659,7 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -5862,9 +5720,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -5990,9 +5845,6 @@
       <c r="O7" t="n">
         <v>43</v>
       </c>
-      <c r="P7" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -6055,11 +5907,7 @@
       <c r="O8" t="n">
         <v>48</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -6245,14 +6093,7 @@
       <c r="O11" t="n">
         <v>39</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6313,9 +6154,6 @@
       </c>
       <c r="O12" t="n">
         <v>34</v>
-      </c>
-      <c r="P12" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -6379,9 +6217,6 @@
       <c r="O13" t="n">
         <v>60</v>
       </c>
-      <c r="P13" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -6444,11 +6279,7 @@
       <c r="O14" t="n">
         <v>48</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
@@ -7033,9 +6864,6 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>52.7</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1203,9 +1203,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1259,9 +1256,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1431,9 +1425,6 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
-      <c r="P17" t="n">
-        <v>22</v>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -2163,14 +2154,7 @@
       <c r="O30" t="n">
         <v>54</v>
       </c>
-      <c r="P30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2228,14 +2212,7 @@
       <c r="O31" t="n">
         <v>45</v>
       </c>
-      <c r="P31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2355,11 +2332,7 @@
       <c r="O33" t="n">
         <v>54</v>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2475,14 +2448,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2656,9 +2622,6 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
-      <c r="P38" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2845,11 +2808,7 @@
       <c r="O41" t="n">
         <v>48</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
@@ -2969,9 +2928,6 @@
       <c r="O43" t="n">
         <v>60</v>
       </c>
-      <c r="P43" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
@@ -3092,9 +3048,6 @@
       <c r="O45" t="n">
         <v>78</v>
       </c>
-      <c r="P45" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
@@ -3273,9 +3226,6 @@
       <c r="O48" t="n">
         <v>60</v>
       </c>
-      <c r="P48" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3392,14 +3342,7 @@
       <c r="O50" t="n">
         <v>54</v>
       </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
     </row>
@@ -3577,9 +3520,6 @@
       <c r="O53" t="n">
         <v>43</v>
       </c>
-      <c r="P53" t="n">
-        <v>22</v>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3638,9 +3578,6 @@
       <c r="O54" t="n">
         <v>43</v>
       </c>
-      <c r="P54" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
@@ -3757,9 +3694,6 @@
       <c r="O56" t="n">
         <v>60</v>
       </c>
-      <c r="P56" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3876,9 +3810,6 @@
       <c r="O58" t="n">
         <v>37</v>
       </c>
-      <c r="P58" t="n">
-        <v>20</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3937,11 +3868,7 @@
       <c r="O59" t="n">
         <v>48</v>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
     </row>
@@ -4173,9 +4100,6 @@
       <c r="O63" t="n">
         <v>43</v>
       </c>
-      <c r="P63" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
@@ -4358,11 +4282,7 @@
       <c r="O66" t="n">
         <v>55</v>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4478,14 +4398,7 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="P68" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4542,9 +4455,6 @@
       </c>
       <c r="O69" t="n">
         <v>45</v>
-      </c>
-      <c r="P69" t="n">
-        <v>17</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4604,14 +4514,7 @@
       <c r="O70" t="n">
         <v>54</v>
       </c>
-      <c r="P70" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4727,11 +4630,7 @@
       <c r="O72" t="n">
         <v>48</v>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
@@ -4851,14 +4750,7 @@
       <c r="O74" t="n">
         <v>44</v>
       </c>
-      <c r="P74" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
     </row>
@@ -4974,9 +4866,6 @@
       <c r="O76" t="n">
         <v>35</v>
       </c>
-      <c r="P76" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
@@ -5039,14 +4928,7 @@
       <c r="O77" t="n">
         <v>42</v>
       </c>
-      <c r="P77" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
@@ -5107,9 +4989,6 @@
       </c>
       <c r="O78" t="n">
         <v>35</v>
-      </c>
-      <c r="P78" t="n">
-        <v>13.3</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -5830,14 +5709,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5898,9 +5770,6 @@
       </c>
       <c r="O3" t="n">
         <v>60</v>
-      </c>
-      <c r="P3" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -6030,11 +5899,7 @@
       <c r="O5" t="n">
         <v>48</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
@@ -6095,9 +5960,6 @@
       </c>
       <c r="O6" t="n">
         <v>60</v>
-      </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -6285,9 +6147,6 @@
       <c r="O9" t="n">
         <v>43</v>
       </c>
-      <c r="P9" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
@@ -6412,11 +6271,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6477,9 +6332,6 @@
       </c>
       <c r="O12" t="n">
         <v>35</v>
-      </c>
-      <c r="P12" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -6543,14 +6395,7 @@
       <c r="O13" t="n">
         <v>42</v>
       </c>
-      <c r="P13" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -7259,9 +7104,6 @@
       <c r="O4" t="n">
         <v>45</v>
       </c>
-      <c r="P4" t="n">
-        <v>52.7</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -7546,11 +7388,7 @@
       <c r="O9" t="n">
         <v>47</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1145,9 +1145,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1259,9 +1256,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1431,9 +1425,6 @@
       <c r="O17" t="n">
         <v>55</v>
       </c>
-      <c r="P17" t="n">
-        <v>22</v>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
@@ -2163,14 +2154,7 @@
       <c r="O30" t="n">
         <v>54</v>
       </c>
-      <c r="P30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2228,14 +2212,7 @@
       <c r="O31" t="n">
         <v>45</v>
       </c>
-      <c r="P31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2413,14 +2390,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2478,11 +2448,7 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2660,9 +2626,6 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
-      <c r="P38" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -2787,14 +2750,7 @@
       <c r="O40" t="n">
         <v>54</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
     </row>
@@ -2910,9 +2866,6 @@
       <c r="O42" t="n">
         <v>79</v>
       </c>
-      <c r="P42" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -3145,9 +3098,6 @@
       <c r="O46" t="n">
         <v>60</v>
       </c>
-      <c r="P46" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
@@ -3450,9 +3400,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
@@ -3573,9 +3520,6 @@
       <c r="O53" t="n">
         <v>60</v>
       </c>
-      <c r="P53" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
@@ -3692,11 +3636,7 @@
       <c r="O55" t="n">
         <v>48</v>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
@@ -3757,9 +3697,6 @@
       </c>
       <c r="O56" t="n">
         <v>43</v>
-      </c>
-      <c r="P56" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3877,9 +3814,6 @@
       <c r="O58" t="n">
         <v>43</v>
       </c>
-      <c r="P58" t="n">
-        <v>22</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -4112,11 +4046,7 @@
       <c r="O62" t="n">
         <v>48</v>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4294,9 +4224,6 @@
       <c r="O65" t="n">
         <v>37</v>
       </c>
-      <c r="P65" t="n">
-        <v>20</v>
-      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -4355,9 +4282,6 @@
       <c r="O66" t="n">
         <v>43</v>
       </c>
-      <c r="P66" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
@@ -4420,11 +4344,7 @@
       <c r="O67" t="n">
         <v>55</v>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4482,14 +4402,7 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="P68" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4605,14 +4518,7 @@
       <c r="O70" t="n">
         <v>41</v>
       </c>
-      <c r="P70" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
@@ -4674,14 +4580,7 @@
       <c r="O71" t="n">
         <v>54</v>
       </c>
-      <c r="P71" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4738,9 +4637,6 @@
       </c>
       <c r="O72" t="n">
         <v>45</v>
-      </c>
-      <c r="P72" t="n">
-        <v>17</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -4974,11 +4870,7 @@
       <c r="O76" t="n">
         <v>48</v>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
@@ -5039,9 +4931,6 @@
       </c>
       <c r="O77" t="n">
         <v>35</v>
-      </c>
-      <c r="P77" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -5878,14 +5767,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6009,9 +5891,6 @@
       <c r="O4" t="n">
         <v>60</v>
       </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -6077,9 +5956,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6267,9 +6143,6 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6332,11 +6205,7 @@
       <c r="O9" t="n">
         <v>48</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6460,9 +6329,6 @@
       <c r="O11" t="n">
         <v>43</v>
       </c>
-      <c r="P11" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
@@ -6525,14 +6391,7 @@
       <c r="O12" t="n">
         <v>41</v>
       </c>
-      <c r="P12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6594,11 +6453,7 @@
       <c r="O13" t="n">
         <v>48</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -6659,9 +6514,6 @@
       </c>
       <c r="O14" t="n">
         <v>35</v>
-      </c>
-      <c r="P14" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -7198,9 +7050,6 @@
       <c r="O2" t="n">
         <v>41</v>
       </c>
-      <c r="P2" t="n">
-        <v>16.7</v>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>ON AD - Sunday special (buy to 8w)</t>
@@ -7373,9 +7222,6 @@
       <c r="O5" t="n">
         <v>45</v>
       </c>
-      <c r="P5" t="n">
-        <v>52.7</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
@@ -7660,11 +7506,7 @@
       <c r="O10" t="n">
         <v>47</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,6 +1092,9 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
+      <c r="P11" t="n">
+        <v>22</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1208,6 +1211,9 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
+      <c r="P13" t="n">
+        <v>22</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1382,6 +1388,9 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
+      <c r="P16" t="n">
+        <v>22</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1846,7 +1855,14 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
@@ -1908,7 +1924,14 @@
       <c r="O25" t="n">
         <v>54</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
     </row>
@@ -2024,7 +2047,14 @@
       <c r="O27" t="n">
         <v>51</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
@@ -2202,6 +2232,9 @@
       <c r="O30" t="n">
         <v>43</v>
       </c>
+      <c r="P30" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
@@ -2438,7 +2471,11 @@
       <c r="O34" t="n">
         <v>52</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2496,7 +2533,14 @@
       <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
     </row>
@@ -2612,7 +2656,11 @@
       <c r="O37" t="n">
         <v>48</v>
       </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2786,6 +2834,9 @@
       <c r="O40" t="n">
         <v>60</v>
       </c>
+      <c r="P40" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
@@ -2848,6 +2899,9 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
+      <c r="P41" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
@@ -2968,7 +3022,14 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3084,7 +3145,11 @@
       <c r="O45" t="n">
         <v>48</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3141,6 +3206,9 @@
       </c>
       <c r="O46" t="n">
         <v>37</v>
+      </c>
+      <c r="P46" t="n">
+        <v>20</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3432,6 +3500,9 @@
       <c r="O51" t="n">
         <v>75</v>
       </c>
+      <c r="P51" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3610,6 +3681,9 @@
       <c r="O54" t="n">
         <v>60</v>
       </c>
+      <c r="P54" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
@@ -3970,7 +4044,14 @@
       <c r="O60" t="n">
         <v>47</v>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
@@ -4032,7 +4113,11 @@
       <c r="O61" t="n">
         <v>55</v>
       </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4090,7 +4175,14 @@
       <c r="O62" t="n">
         <v>42</v>
       </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Case 1</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4147,6 +4239,9 @@
       </c>
       <c r="O63" t="n">
         <v>45</v>
+      </c>
+      <c r="P63" t="n">
+        <v>17</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -4322,7 +4417,14 @@
       <c r="O66" t="n">
         <v>54</v>
       </c>
-      <c r="Q66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4442,6 +4544,9 @@
       <c r="O68" t="n">
         <v>82</v>
       </c>
+      <c r="P68" t="n">
+        <v>24.9</v>
+      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -4500,6 +4605,9 @@
       <c r="O69" t="n">
         <v>60</v>
       </c>
+      <c r="P69" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
@@ -4562,6 +4670,9 @@
       <c r="O70" t="n">
         <v>43</v>
       </c>
+      <c r="P70" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
@@ -4624,7 +4735,14 @@
       <c r="O71" t="n">
         <v>47</v>
       </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Kiwi Strawberry (Pink)</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4682,7 +4800,14 @@
       <c r="O72" t="n">
         <v>44</v>
       </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Blackberry Lemon (Purple)</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -4802,6 +4927,9 @@
       <c r="O74" t="n">
         <v>36</v>
       </c>
+      <c r="P74" t="n">
+        <v>25.7</v>
+      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
@@ -4864,7 +4992,14 @@
       <c r="O75" t="n">
         <v>54</v>
       </c>
-      <c r="Q75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -4922,7 +5057,14 @@
       <c r="O76" t="n">
         <v>54</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -4980,7 +5122,11 @@
       <c r="O77" t="n">
         <v>48</v>
       </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5096,9 +5242,12 @@
       <c r="O79" t="n">
         <v>39</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
         </is>
       </c>
       <c r="R79" t="inlineStr"/>
@@ -5352,9 +5501,12 @@
       <c r="O83" t="n">
         <v>44</v>
       </c>
+      <c r="P83" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R83" t="inlineStr"/>
@@ -5839,7 +5991,14 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -5901,7 +6060,14 @@
       <c r="O3" t="n">
         <v>51</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6025,6 +6191,9 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
+      <c r="P5" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6087,6 +6256,9 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
+      <c r="P6" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6211,6 +6383,9 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
+      <c r="P8" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6397,7 +6572,14 @@
       <c r="O11" t="n">
         <v>47</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6521,6 +6703,9 @@
       <c r="O13" t="n">
         <v>60</v>
       </c>
+      <c r="P13" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -6583,6 +6768,9 @@
       <c r="O14" t="n">
         <v>43</v>
       </c>
+      <c r="P14" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -6707,6 +6895,9 @@
       <c r="O16" t="n">
         <v>36</v>
       </c>
+      <c r="P16" t="n">
+        <v>25.7</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
@@ -6769,9 +6960,12 @@
       <c r="O17" t="n">
         <v>39</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -7025,9 +7219,12 @@
       <c r="O21" t="n">
         <v>44</v>
       </c>
+      <c r="P21" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -7950,7 +8147,11 @@
       <c r="O10" t="n">
         <v>48</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8230,7 +8431,11 @@
       <c r="O15" t="n">
         <v>47</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Case 1 Upfront</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1150,9 +1150,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1211,9 +1208,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1504,9 +1498,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -1855,14 +1846,7 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="P24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
@@ -1924,14 +1908,7 @@
       <c r="O25" t="n">
         <v>54</v>
       </c>
-      <c r="P25" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
     </row>
@@ -2105,14 +2082,7 @@
       <c r="O28" t="n">
         <v>51</v>
       </c>
-      <c r="P28" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
@@ -2410,11 +2380,7 @@
       <c r="O33" t="n">
         <v>52</v>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
     </row>
@@ -2530,9 +2496,6 @@
       <c r="O35" t="n">
         <v>43</v>
       </c>
-      <c r="P35" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -2591,14 +2554,7 @@
       <c r="O36" t="n">
         <v>54</v>
       </c>
-      <c r="P36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2656,11 +2612,7 @@
       <c r="O37" t="n">
         <v>48</v>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2892,9 +2844,6 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
-      <c r="P41" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
@@ -2957,9 +2906,6 @@
       <c r="O42" t="n">
         <v>60</v>
       </c>
-      <c r="P42" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
@@ -3138,14 +3084,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3203,11 +3142,7 @@
       <c r="O46" t="n">
         <v>48</v>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3264,9 +3199,6 @@
       </c>
       <c r="O47" t="n">
         <v>76</v>
-      </c>
-      <c r="P47" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3326,9 +3258,6 @@
       <c r="O48" t="n">
         <v>37</v>
       </c>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -3445,9 +3374,6 @@
       <c r="O50" t="n">
         <v>60</v>
       </c>
-      <c r="P50" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
@@ -3746,9 +3672,6 @@
       <c r="O55" t="n">
         <v>45</v>
       </c>
-      <c r="P55" t="n">
-        <v>17</v>
-      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3989,14 +3912,7 @@
       <c r="O59" t="n">
         <v>47</v>
       </c>
-      <c r="P59" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
@@ -4116,14 +4032,7 @@
       <c r="O61" t="n">
         <v>54</v>
       </c>
-      <c r="P61" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4301,11 +4210,7 @@
       <c r="O64" t="n">
         <v>55</v>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
     </row>
@@ -4362,9 +4267,6 @@
       </c>
       <c r="O65" t="n">
         <v>82</v>
-      </c>
-      <c r="P65" t="n">
-        <v>24.9</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -4424,9 +4326,6 @@
       <c r="O66" t="n">
         <v>60</v>
       </c>
-      <c r="P66" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
@@ -4485,14 +4384,7 @@
       <c r="O67" t="n">
         <v>42</v>
       </c>
-      <c r="P67" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4549,9 +4441,6 @@
       </c>
       <c r="O68" t="n">
         <v>43</v>
-      </c>
-      <c r="P68" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4673,14 +4562,7 @@
       <c r="O70" t="n">
         <v>47</v>
       </c>
-      <c r="P70" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4738,11 +4620,7 @@
       <c r="O71" t="n">
         <v>47</v>
       </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4800,14 +4678,7 @@
       <c r="O72" t="n">
         <v>44</v>
       </c>
-      <c r="P72" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -4864,9 +4735,6 @@
       </c>
       <c r="O73" t="n">
         <v>35</v>
-      </c>
-      <c r="P73" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -5054,14 +4922,7 @@
       <c r="O76" t="n">
         <v>54</v>
       </c>
-      <c r="P76" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5119,14 +4980,7 @@
       <c r="O77" t="n">
         <v>54</v>
       </c>
-      <c r="P77" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5358,12 +5212,9 @@
       <c r="O81" t="n">
         <v>39</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R81" t="inlineStr"/>
@@ -5555,12 +5406,9 @@
       <c r="O84" t="n">
         <v>44</v>
       </c>
-      <c r="P84" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R84" t="inlineStr"/>
@@ -5983,14 +5831,7 @@
       <c r="O2" t="n">
         <v>45</v>
       </c>
-      <c r="P2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -6052,14 +5893,7 @@
       <c r="O3" t="n">
         <v>51</v>
       </c>
-      <c r="P3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6183,9 +6017,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6248,9 +6079,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6313,9 +6141,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -6564,14 +6389,7 @@
       <c r="O11" t="n">
         <v>47</v>
       </c>
-      <c r="P11" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6695,9 +6513,6 @@
       <c r="O13" t="n">
         <v>43</v>
       </c>
-      <c r="P13" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -6760,9 +6575,6 @@
       <c r="O14" t="n">
         <v>35</v>
       </c>
-      <c r="P14" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -6949,12 +6761,9 @@
       <c r="O17" t="n">
         <v>39</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); Pallet Orders</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -7146,12 +6955,9 @@
       <c r="O20" t="n">
         <v>44</v>
       </c>
-      <c r="P20" t="n">
-        <v>20.8</v>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>ON AD - weekly special (buy to 4.5w); 3cs Min Buy</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -8012,11 +7818,7 @@
       <c r="O10" t="n">
         <v>48</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8296,11 +8098,7 @@
       <c r="O15" t="n">
         <v>47</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1212,9 +1212,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1273,9 +1270,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1566,9 +1560,6 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="P19" t="n">
-        <v>22</v>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -1917,14 +1908,7 @@
       <c r="O25" t="n">
         <v>45</v>
       </c>
-      <c r="P25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
@@ -2044,14 +2028,7 @@
       <c r="O27" t="n">
         <v>51</v>
       </c>
-      <c r="P27" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
@@ -2171,11 +2148,7 @@
       <c r="O29" t="n">
         <v>52</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
     </row>
@@ -2291,9 +2264,6 @@
       <c r="O31" t="n">
         <v>79</v>
       </c>
-      <c r="P31" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
@@ -2352,9 +2322,6 @@
       <c r="O32" t="n">
         <v>43</v>
       </c>
-      <c r="P32" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
@@ -2529,9 +2496,6 @@
       <c r="O35" t="n">
         <v>60</v>
       </c>
-      <c r="P35" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
@@ -2594,9 +2558,6 @@
       <c r="O36" t="n">
         <v>60</v>
       </c>
-      <c r="P36" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
@@ -2659,14 +2620,7 @@
       <c r="O37" t="n">
         <v>54</v>
       </c>
-      <c r="P37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2782,9 +2736,6 @@
       <c r="O39" t="n">
         <v>60</v>
       </c>
-      <c r="P39" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
@@ -2909,9 +2860,6 @@
       <c r="O41" t="n">
         <v>37</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2970,11 +2918,7 @@
       <c r="O42" t="n">
         <v>48</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -3090,14 +3034,7 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3213,11 +3150,7 @@
       <c r="O46" t="n">
         <v>48</v>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3275,14 +3208,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3398,14 +3324,7 @@
       <c r="O49" t="n">
         <v>47</v>
       </c>
-      <c r="P49" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
@@ -3529,9 +3448,6 @@
       <c r="O51" t="n">
         <v>83</v>
       </c>
-      <c r="P51" t="n">
-        <v>24.9</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3590,9 +3506,6 @@
       <c r="O52" t="n">
         <v>60</v>
       </c>
-      <c r="P52" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3891,9 +3804,6 @@
       <c r="O57" t="n">
         <v>43</v>
       </c>
-      <c r="P57" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
@@ -4072,14 +3982,7 @@
       <c r="O60" t="n">
         <v>42</v>
       </c>
-      <c r="P60" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4199,11 +4102,7 @@
       <c r="O62" t="n">
         <v>47</v>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
     </row>
@@ -4261,11 +4160,7 @@
       <c r="O63" t="n">
         <v>55</v>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4443,14 +4338,7 @@
       <c r="O66" t="n">
         <v>39</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
@@ -4511,9 +4399,6 @@
       </c>
       <c r="O67" t="n">
         <v>45</v>
-      </c>
-      <c r="P67" t="n">
-        <v>17</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4751,14 +4636,7 @@
       <c r="O71" t="n">
         <v>54</v>
       </c>
-      <c r="P71" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -4816,14 +4694,7 @@
       <c r="O72" t="n">
         <v>54</v>
       </c>
-      <c r="P72" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -5001,14 +4872,7 @@
       <c r="O75" t="n">
         <v>54</v>
       </c>
-      <c r="P75" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -5240,9 +5104,6 @@
       <c r="O79" t="n">
         <v>43</v>
       </c>
-      <c r="P79" t="n">
-        <v>22</v>
-      </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
@@ -5359,14 +5220,7 @@
       <c r="O81" t="n">
         <v>44</v>
       </c>
-      <c r="P81" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
     </row>
@@ -5481,9 +5335,6 @@
       </c>
       <c r="O83" t="n">
         <v>35</v>
-      </c>
-      <c r="P83" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -6030,14 +5881,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6099,14 +5943,7 @@
       <c r="O4" t="n">
         <v>51</v>
       </c>
-      <c r="P4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6167,9 +6004,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6233,9 +6067,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6298,9 +6129,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="P7" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -6425,14 +6253,7 @@
       <c r="O9" t="n">
         <v>47</v>
       </c>
-      <c r="P9" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6680,9 +6501,6 @@
       <c r="O13" t="n">
         <v>43</v>
       </c>
-      <c r="P13" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -6869,14 +6687,7 @@
       <c r="O16" t="n">
         <v>39</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
@@ -7061,9 +6872,6 @@
       </c>
       <c r="O19" t="n">
         <v>35</v>
-      </c>
-      <c r="P19" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7928,11 +7736,7 @@
       <c r="O10" t="n">
         <v>48</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8212,11 +8016,7 @@
       <c r="O15" t="n">
         <v>47</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1324,9 +1324,6 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
-      <c r="P15" t="n">
-        <v>22</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1385,9 +1382,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="P16" t="n">
-        <v>22</v>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1620,9 +1614,6 @@
       <c r="O20" t="n">
         <v>55</v>
       </c>
-      <c r="P20" t="n">
-        <v>22</v>
-      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
@@ -2033,14 +2024,7 @@
       <c r="O27" t="n">
         <v>45</v>
       </c>
-      <c r="P27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
@@ -2160,14 +2144,7 @@
       <c r="O29" t="n">
         <v>51</v>
       </c>
-      <c r="P29" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
@@ -2287,11 +2264,7 @@
       <c r="O31" t="n">
         <v>53</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2348,9 +2321,6 @@
       </c>
       <c r="O32" t="n">
         <v>43</v>
-      </c>
-      <c r="P32" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2410,9 +2380,6 @@
       <c r="O33" t="n">
         <v>60</v>
       </c>
-      <c r="P33" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
@@ -2591,9 +2558,6 @@
       <c r="O36" t="n">
         <v>60</v>
       </c>
-      <c r="P36" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
@@ -2656,11 +2620,7 @@
       <c r="O37" t="n">
         <v>48</v>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
     </row>
@@ -2892,9 +2852,6 @@
       <c r="O41" t="n">
         <v>73</v>
       </c>
-      <c r="P41" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
@@ -2953,14 +2910,7 @@
       <c r="O42" t="n">
         <v>47</v>
       </c>
-      <c r="P42" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
@@ -3022,11 +2972,7 @@
       <c r="O43" t="n">
         <v>48</v>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3084,14 +3030,7 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3211,9 +3150,6 @@
       <c r="O46" t="n">
         <v>37</v>
       </c>
-      <c r="P46" t="n">
-        <v>20</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3272,14 +3208,7 @@
       <c r="O47" t="n">
         <v>39</v>
       </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3341,14 +3270,7 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3406,14 +3328,7 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="P49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
     </row>
@@ -3470,9 +3385,6 @@
       </c>
       <c r="O50" t="n">
         <v>60</v>
-      </c>
-      <c r="P50" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3772,9 +3684,6 @@
       <c r="O55" t="n">
         <v>83</v>
       </c>
-      <c r="P55" t="n">
-        <v>24.9</v>
-      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
@@ -3833,9 +3742,6 @@
       <c r="O56" t="n">
         <v>60</v>
       </c>
-      <c r="P56" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
@@ -3894,11 +3800,7 @@
       <c r="O57" t="n">
         <v>55</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
     </row>
@@ -4138,9 +4040,6 @@
       <c r="O61" t="n">
         <v>43</v>
       </c>
-      <c r="P61" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
@@ -4381,9 +4280,6 @@
       <c r="O65" t="n">
         <v>45</v>
       </c>
-      <c r="P65" t="n">
-        <v>17</v>
-      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
@@ -4620,14 +4516,7 @@
       <c r="O69" t="n">
         <v>54</v>
       </c>
-      <c r="P69" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
     </row>
@@ -4685,11 +4574,7 @@
       <c r="O70" t="n">
         <v>47</v>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
     </row>
@@ -4805,14 +4690,7 @@
       <c r="O72" t="n">
         <v>54</v>
       </c>
-      <c r="P72" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -4986,14 +4864,7 @@
       <c r="O75" t="n">
         <v>44</v>
       </c>
-      <c r="P75" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -5225,14 +5096,7 @@
       <c r="O79" t="n">
         <v>54</v>
       </c>
-      <c r="P79" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5289,9 +5153,6 @@
       </c>
       <c r="O80" t="n">
         <v>36</v>
-      </c>
-      <c r="P80" t="n">
-        <v>25.7</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -5355,14 +5216,7 @@
       <c r="O81" t="n">
         <v>47</v>
       </c>
-      <c r="P81" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
     </row>
@@ -5482,11 +5336,7 @@
       <c r="O83" t="n">
         <v>73</v>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>60 Day Reorder Time</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
     </row>
@@ -5907,9 +5757,6 @@
       </c>
       <c r="O90" t="n">
         <v>60</v>
-      </c>
-      <c r="P90" t="n">
-        <v>13</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -6398,14 +6245,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6467,14 +6307,7 @@
       <c r="O4" t="n">
         <v>51</v>
       </c>
-      <c r="P4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -6535,9 +6368,6 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6601,9 +6431,6 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6666,14 +6493,7 @@
       <c r="O7" t="n">
         <v>47</v>
       </c>
-      <c r="P7" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
@@ -6797,14 +6617,7 @@
       <c r="O9" t="n">
         <v>39</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6865,9 +6678,6 @@
       </c>
       <c r="O10" t="n">
         <v>60</v>
-      </c>
-      <c r="P10" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -7117,9 +6927,6 @@
       <c r="O14" t="n">
         <v>43</v>
       </c>
-      <c r="P14" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -7306,9 +7113,6 @@
       <c r="O17" t="n">
         <v>36</v>
       </c>
-      <c r="P17" t="n">
-        <v>25.7</v>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
@@ -7622,9 +7426,6 @@
       </c>
       <c r="O22" t="n">
         <v>60</v>
-      </c>
-      <c r="P22" t="n">
-        <v>13</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -8489,11 +8290,7 @@
       <c r="O10" t="n">
         <v>48</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8549,11 +8346,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8833,11 +8626,7 @@
       <c r="O16" t="n">
         <v>47</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1324,6 +1324,9 @@
       <c r="O15" t="n">
         <v>55</v>
       </c>
+      <c r="P15" t="n">
+        <v>22</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
@@ -1382,6 +1385,9 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
+      <c r="P16" t="n">
+        <v>22</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1498,6 +1504,9 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
+      <c r="P18" t="n">
+        <v>22</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2082,7 +2091,14 @@
       <c r="O28" t="n">
         <v>45</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
@@ -2202,7 +2218,11 @@
       <c r="O30" t="n">
         <v>53</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2260,7 +2280,14 @@
       <c r="O31" t="n">
         <v>51</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
@@ -2321,6 +2348,9 @@
       </c>
       <c r="O32" t="n">
         <v>60</v>
+      </c>
+      <c r="P32" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2384,6 +2414,9 @@
       <c r="O33" t="n">
         <v>43</v>
       </c>
+      <c r="P33" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
@@ -2558,6 +2591,9 @@
       <c r="O36" t="n">
         <v>60</v>
       </c>
+      <c r="P36" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
@@ -2740,7 +2776,11 @@
       <c r="O39" t="n">
         <v>48</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
     </row>
@@ -2914,7 +2954,14 @@
       <c r="O42" t="n">
         <v>39</v>
       </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
@@ -3038,7 +3085,14 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
     </row>
@@ -3095,6 +3149,9 @@
       </c>
       <c r="O45" t="n">
         <v>60</v>
+      </c>
+      <c r="P45" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3220,7 +3277,11 @@
       <c r="O47" t="n">
         <v>48</v>
       </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3277,6 +3338,9 @@
       </c>
       <c r="O48" t="n">
         <v>74</v>
+      </c>
+      <c r="P48" t="n">
+        <v>13.7</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3336,7 +3400,14 @@
       <c r="O49" t="n">
         <v>47</v>
       </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
@@ -3456,6 +3527,9 @@
       <c r="O51" t="n">
         <v>37</v>
       </c>
+      <c r="P51" t="n">
+        <v>20</v>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3576,7 +3650,14 @@
       <c r="O53" t="n">
         <v>54</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3634,7 +3715,14 @@
       <c r="O54" t="n">
         <v>54</v>
       </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3808,6 +3896,9 @@
       <c r="O57" t="n">
         <v>60</v>
       </c>
+      <c r="P57" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
@@ -4164,7 +4255,11 @@
       <c r="O63" t="n">
         <v>55</v>
       </c>
-      <c r="Q63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4280,7 +4375,14 @@
       <c r="O65" t="n">
         <v>54</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
     </row>
@@ -4337,6 +4439,9 @@
       </c>
       <c r="O66" t="n">
         <v>43</v>
+      </c>
+      <c r="P66" t="n">
+        <v>21.1</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4400,6 +4505,9 @@
       <c r="O67" t="n">
         <v>45</v>
       </c>
+      <c r="P67" t="n">
+        <v>17</v>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
@@ -4458,6 +4566,9 @@
       <c r="O68" t="n">
         <v>83</v>
       </c>
+      <c r="P68" t="n">
+        <v>24.9</v>
+      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
@@ -4822,7 +4933,14 @@
       <c r="O74" t="n">
         <v>54</v>
       </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
     </row>
@@ -4938,7 +5056,11 @@
       <c r="O76" t="n">
         <v>47</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5116,7 +5238,14 @@
       <c r="O79" t="n">
         <v>54</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5348,7 +5477,11 @@
       <c r="O83" t="n">
         <v>47</v>
       </c>
-      <c r="Q83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
     </row>
@@ -5406,7 +5539,14 @@
       <c r="O84" t="n">
         <v>44</v>
       </c>
-      <c r="Q84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Blackberry Lemon (Purple)</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
     </row>
@@ -5463,6 +5603,9 @@
       </c>
       <c r="O85" t="n">
         <v>53</v>
+      </c>
+      <c r="P85" t="n">
+        <v>21.1</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5526,6 +5669,9 @@
       <c r="O86" t="n">
         <v>36</v>
       </c>
+      <c r="P86" t="n">
+        <v>25.7</v>
+      </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
@@ -5588,7 +5734,14 @@
       <c r="O87" t="n">
         <v>45</v>
       </c>
-      <c r="Q87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
@@ -5650,7 +5803,11 @@
       <c r="O88" t="n">
         <v>73</v>
       </c>
-      <c r="Q88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>60 Day Reorder Time</t>
+        </is>
+      </c>
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
     </row>
@@ -5708,7 +5865,11 @@
       <c r="O89" t="n">
         <v>48</v>
       </c>
-      <c r="Q89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
     </row>
@@ -5766,7 +5927,14 @@
       <c r="O90" t="n">
         <v>47</v>
       </c>
-      <c r="Q90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Kiwi Strawberry (Pink)</t>
+        </is>
+      </c>
       <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr"/>
     </row>
@@ -5940,7 +6108,14 @@
       <c r="O93" t="n">
         <v>54</v>
       </c>
-      <c r="Q93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
     </row>
@@ -6403,6 +6578,9 @@
       </c>
       <c r="O101" t="n">
         <v>61</v>
+      </c>
+      <c r="P101" t="n">
+        <v>13</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -6953,7 +7131,14 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -7015,7 +7200,14 @@
       <c r="O4" t="n">
         <v>51</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -7076,6 +7268,9 @@
       </c>
       <c r="O5" t="n">
         <v>60</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -7139,6 +7334,9 @@
       <c r="O6" t="n">
         <v>60</v>
       </c>
+      <c r="P6" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -7263,7 +7461,14 @@
       <c r="O8" t="n">
         <v>39</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
@@ -7387,6 +7592,9 @@
       <c r="O10" t="n">
         <v>60</v>
       </c>
+      <c r="P10" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
@@ -7511,7 +7719,14 @@
       <c r="O12" t="n">
         <v>47</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -7759,6 +7974,9 @@
       <c r="O16" t="n">
         <v>43</v>
       </c>
+      <c r="P16" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
@@ -8073,6 +8291,9 @@
       <c r="O21" t="n">
         <v>53</v>
       </c>
+      <c r="P21" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
@@ -8135,6 +8356,9 @@
       <c r="O22" t="n">
         <v>36</v>
       </c>
+      <c r="P22" t="n">
+        <v>25.7</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
@@ -8197,7 +8421,14 @@
       <c r="O23" t="n">
         <v>45</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
@@ -8258,6 +8489,9 @@
       </c>
       <c r="O24" t="n">
         <v>61</v>
+      </c>
+      <c r="P24" t="n">
+        <v>13</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -9184,7 +9418,11 @@
       <c r="O10" t="n">
         <v>48</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9240,7 +9478,11 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9296,7 +9538,11 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9464,7 +9710,14 @@
       <c r="O15" t="n">
         <v>54</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9744,7 +9997,11 @@
       <c r="O20" t="n">
         <v>47</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Case 1 Upfront</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,9 +1092,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1269,9 +1266,6 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
-        <v>22</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1562,9 +1556,6 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
-      <c r="P19" t="n">
-        <v>22</v>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -1859,14 +1850,7 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="P24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
@@ -1986,11 +1970,7 @@
       <c r="O26" t="n">
         <v>53</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
@@ -2047,9 +2027,6 @@
       </c>
       <c r="O27" t="n">
         <v>60</v>
-      </c>
-      <c r="P27" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -2345,9 +2322,6 @@
       <c r="O32" t="n">
         <v>60</v>
       </c>
-      <c r="P32" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
@@ -2410,9 +2384,6 @@
       <c r="O33" t="n">
         <v>43</v>
       </c>
-      <c r="P33" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
@@ -2475,14 +2446,7 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="P34" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2598,11 +2562,7 @@
       <c r="O36" t="n">
         <v>48</v>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2838,9 +2798,6 @@
       <c r="O40" t="n">
         <v>37</v>
       </c>
-      <c r="P40" t="n">
-        <v>20</v>
-      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2899,9 +2856,6 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
-      <c r="P41" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
@@ -3084,14 +3038,7 @@
       <c r="O44" t="n">
         <v>47</v>
       </c>
-      <c r="P44" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3153,14 +3100,7 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3217,9 +3157,6 @@
       </c>
       <c r="O46" t="n">
         <v>45</v>
-      </c>
-      <c r="P46" t="n">
-        <v>17</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3279,14 +3216,7 @@
       <c r="O47" t="n">
         <v>51</v>
       </c>
-      <c r="P47" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3348,14 +3278,7 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="P48" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3529,9 +3452,6 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
-      <c r="P51" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3590,14 +3510,7 @@
       <c r="O52" t="n">
         <v>39</v>
       </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
@@ -3659,11 +3572,7 @@
       <c r="O53" t="n">
         <v>48</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -3903,9 +3812,6 @@
       <c r="O57" t="n">
         <v>43</v>
       </c>
-      <c r="P57" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
@@ -3968,9 +3874,6 @@
       <c r="O58" t="n">
         <v>72</v>
       </c>
-      <c r="P58" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -4087,9 +3990,6 @@
       <c r="O60" t="n">
         <v>84</v>
       </c>
-      <c r="P60" t="n">
-        <v>24.9</v>
-      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4148,14 +4048,7 @@
       <c r="O61" t="n">
         <v>54</v>
       </c>
-      <c r="P61" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4275,11 +4168,7 @@
       <c r="O63" t="n">
         <v>55</v>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4453,14 +4342,7 @@
       <c r="O66" t="n">
         <v>54</v>
       </c>
-      <c r="P66" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4518,11 +4400,7 @@
       <c r="O67" t="n">
         <v>47</v>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4580,14 +4458,7 @@
       <c r="O68" t="n">
         <v>44</v>
       </c>
-      <c r="P68" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4823,14 +4694,7 @@
       <c r="O72" t="n">
         <v>45</v>
       </c>
-      <c r="P72" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
@@ -4892,14 +4756,7 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="P73" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
     </row>
@@ -4957,14 +4814,7 @@
       <c r="O74" t="n">
         <v>47</v>
       </c>
-      <c r="P74" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
     </row>
@@ -5080,11 +4930,7 @@
       <c r="O76" t="n">
         <v>48</v>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5142,11 +4988,7 @@
       <c r="O77" t="n">
         <v>47</v>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5204,14 +5046,7 @@
       <c r="O78" t="n">
         <v>54</v>
       </c>
-      <c r="P78" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
@@ -5272,9 +5107,6 @@
       </c>
       <c r="O79" t="n">
         <v>43</v>
-      </c>
-      <c r="P79" t="n">
-        <v>22</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -5689,9 +5521,6 @@
       </c>
       <c r="O86" t="n">
         <v>61</v>
-      </c>
-      <c r="P86" t="n">
-        <v>13</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6180,14 +6009,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6248,9 +6070,6 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -6314,9 +6133,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6379,9 +6195,6 @@
       <c r="O6" t="n">
         <v>43</v>
       </c>
-      <c r="P6" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6506,9 +6319,6 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6633,14 +6443,7 @@
       <c r="O10" t="n">
         <v>47</v>
       </c>
-      <c r="P10" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
@@ -6702,14 +6505,7 @@
       <c r="O11" t="n">
         <v>51</v>
       </c>
-      <c r="P11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6771,14 +6567,7 @@
       <c r="O12" t="n">
         <v>39</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6840,11 +6629,7 @@
       <c r="O13" t="n">
         <v>48</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -6968,9 +6753,6 @@
       <c r="O15" t="n">
         <v>43</v>
       </c>
-      <c r="P15" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
@@ -7157,14 +6939,7 @@
       <c r="O18" t="n">
         <v>45</v>
       </c>
-      <c r="P18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
@@ -7226,14 +7001,7 @@
       <c r="O19" t="n">
         <v>54</v>
       </c>
-      <c r="P19" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
@@ -7360,9 +7128,6 @@
       </c>
       <c r="O21" t="n">
         <v>61</v>
-      </c>
-      <c r="P21" t="n">
-        <v>13</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -8283,11 +8048,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8455,14 +8216,7 @@
       <c r="O14" t="n">
         <v>54</v>
       </c>
-      <c r="P14" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8742,11 +8496,7 @@
       <c r="O19" t="n">
         <v>47</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,6 +1092,9 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
+      <c r="P11" t="n">
+        <v>22</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1266,6 +1269,9 @@
       <c r="O14" t="n">
         <v>55</v>
       </c>
+      <c r="P14" t="n">
+        <v>22</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
@@ -1556,6 +1562,9 @@
       <c r="O19" t="n">
         <v>55</v>
       </c>
+      <c r="P19" t="n">
+        <v>22</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
@@ -1850,7 +1859,14 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
@@ -1970,7 +1986,11 @@
       <c r="O26" t="n">
         <v>53</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
@@ -2027,6 +2047,9 @@
       </c>
       <c r="O27" t="n">
         <v>60</v>
+      </c>
+      <c r="P27" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -2322,6 +2345,9 @@
       <c r="O32" t="n">
         <v>60</v>
       </c>
+      <c r="P32" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
@@ -2384,6 +2410,9 @@
       <c r="O33" t="n">
         <v>43</v>
       </c>
+      <c r="P33" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
@@ -2446,7 +2475,14 @@
       <c r="O34" t="n">
         <v>54</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
     </row>
@@ -2562,7 +2598,11 @@
       <c r="O36" t="n">
         <v>48</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -2798,6 +2838,9 @@
       <c r="O40" t="n">
         <v>37</v>
       </c>
+      <c r="P40" t="n">
+        <v>20</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
@@ -2856,6 +2899,9 @@
       <c r="O41" t="n">
         <v>60</v>
       </c>
+      <c r="P41" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
@@ -3038,7 +3084,14 @@
       <c r="O44" t="n">
         <v>47</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3100,7 +3153,14 @@
       <c r="O45" t="n">
         <v>54</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
     </row>
@@ -3157,6 +3217,9 @@
       </c>
       <c r="O46" t="n">
         <v>45</v>
+      </c>
+      <c r="P46" t="n">
+        <v>17</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3216,7 +3279,14 @@
       <c r="O47" t="n">
         <v>51</v>
       </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
@@ -3278,7 +3348,14 @@
       <c r="O48" t="n">
         <v>54</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
     </row>
@@ -3452,6 +3529,9 @@
       <c r="O51" t="n">
         <v>60</v>
       </c>
+      <c r="P51" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3510,7 +3590,14 @@
       <c r="O52" t="n">
         <v>39</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
@@ -3572,7 +3659,11 @@
       <c r="O53" t="n">
         <v>48</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -3812,6 +3903,9 @@
       <c r="O57" t="n">
         <v>43</v>
       </c>
+      <c r="P57" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
@@ -3874,6 +3968,9 @@
       <c r="O58" t="n">
         <v>72</v>
       </c>
+      <c r="P58" t="n">
+        <v>13.7</v>
+      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -3990,6 +4087,9 @@
       <c r="O60" t="n">
         <v>84</v>
       </c>
+      <c r="P60" t="n">
+        <v>24.9</v>
+      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
@@ -4048,7 +4148,14 @@
       <c r="O61" t="n">
         <v>54</v>
       </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
     </row>
@@ -4168,7 +4275,11 @@
       <c r="O63" t="n">
         <v>55</v>
       </c>
-      <c r="Q63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Direct Ship to Blaine</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4342,7 +4453,14 @@
       <c r="O66" t="n">
         <v>54</v>
       </c>
-      <c r="Q66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
     </row>
@@ -4400,7 +4518,11 @@
       <c r="O67" t="n">
         <v>47</v>
       </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4458,7 +4580,14 @@
       <c r="O68" t="n">
         <v>44</v>
       </c>
-      <c r="Q68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Blackberry Lemon (Purple)</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
     </row>
@@ -4694,7 +4823,14 @@
       <c r="O72" t="n">
         <v>45</v>
       </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
@@ -4756,7 +4892,14 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="Q73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
     </row>
@@ -4814,7 +4957,14 @@
       <c r="O74" t="n">
         <v>47</v>
       </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Kiwi Strawberry (Pink)</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
     </row>
@@ -4930,7 +5080,11 @@
       <c r="O76" t="n">
         <v>48</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -4988,7 +5142,11 @@
       <c r="O77" t="n">
         <v>47</v>
       </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5046,7 +5204,14 @@
       <c r="O78" t="n">
         <v>54</v>
       </c>
-      <c r="Q78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
@@ -5107,6 +5272,9 @@
       </c>
       <c r="O79" t="n">
         <v>43</v>
+      </c>
+      <c r="P79" t="n">
+        <v>22</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -5521,6 +5689,9 @@
       </c>
       <c r="O86" t="n">
         <v>61</v>
+      </c>
+      <c r="P86" t="n">
+        <v>13</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6009,7 +6180,14 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6070,6 +6248,9 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
+      </c>
+      <c r="P4" t="n">
+        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -6133,6 +6314,9 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
+      <c r="P5" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6195,6 +6379,9 @@
       <c r="O6" t="n">
         <v>43</v>
       </c>
+      <c r="P6" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -6319,6 +6506,9 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
+      <c r="P8" t="n">
+        <v>23.1</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6443,7 +6633,14 @@
       <c r="O10" t="n">
         <v>47</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>15c</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
@@ -6505,7 +6702,14 @@
       <c r="O11" t="n">
         <v>51</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Extra on 12pk to make up for 4pk</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6567,7 +6771,14 @@
       <c r="O12" t="n">
         <v>39</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Pallet Orders</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6629,7 +6840,11 @@
       <c r="O13" t="n">
         <v>48</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
@@ -6753,6 +6968,9 @@
       <c r="O15" t="n">
         <v>43</v>
       </c>
+      <c r="P15" t="n">
+        <v>21.1</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
@@ -6939,7 +7157,14 @@
       <c r="O18" t="n">
         <v>45</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
@@ -7001,7 +7226,14 @@
       <c r="O19" t="n">
         <v>54</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
@@ -7128,6 +7360,9 @@
       </c>
       <c r="O21" t="n">
         <v>61</v>
+      </c>
+      <c r="P21" t="n">
+        <v>13</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -8048,7 +8283,11 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Quarterly buy</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8216,7 +8455,14 @@
       <c r="O14" t="n">
         <v>54</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>$200 order qty per store</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8496,7 +8742,11 @@
       <c r="O19" t="n">
         <v>47</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Case 1 Upfront</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,9 +1092,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1153,9 +1150,6 @@
       <c r="O12" t="n">
         <v>55</v>
       </c>
-      <c r="P12" t="n">
-        <v>22</v>
-      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
@@ -1504,9 +1498,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -1859,14 +1850,7 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="P24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
@@ -1986,11 +1970,7 @@
       <c r="O26" t="n">
         <v>53</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
@@ -2047,9 +2027,6 @@
       </c>
       <c r="O27" t="n">
         <v>60</v>
-      </c>
-      <c r="P27" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -2113,9 +2090,6 @@
       <c r="O28" t="n">
         <v>60</v>
       </c>
-      <c r="P28" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
@@ -2294,14 +2268,7 @@
       <c r="O31" t="n">
         <v>54</v>
       </c>
-      <c r="P31" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
     </row>
@@ -2533,9 +2500,6 @@
       <c r="O35" t="n">
         <v>37</v>
       </c>
-      <c r="P35" t="n">
-        <v>20</v>
-      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
@@ -2718,9 +2682,6 @@
       <c r="O38" t="n">
         <v>60</v>
       </c>
-      <c r="P38" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -2783,14 +2744,7 @@
       <c r="O39" t="n">
         <v>39</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2851,9 +2805,6 @@
       </c>
       <c r="O40" t="n">
         <v>43</v>
-      </c>
-      <c r="P40" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2917,14 +2868,7 @@
       <c r="O41" t="n">
         <v>54</v>
       </c>
-      <c r="P41" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -2982,11 +2926,7 @@
       <c r="O42" t="n">
         <v>48</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
     </row>
@@ -3043,9 +2983,6 @@
       </c>
       <c r="O43" t="n">
         <v>45</v>
-      </c>
-      <c r="P43" t="n">
-        <v>17</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -3105,14 +3042,7 @@
       <c r="O44" t="n">
         <v>47</v>
       </c>
-      <c r="P44" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3174,14 +3104,7 @@
       <c r="O45" t="n">
         <v>51</v>
       </c>
-      <c r="P45" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
@@ -3305,14 +3228,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3602,9 +3518,6 @@
       <c r="O52" t="n">
         <v>60</v>
       </c>
-      <c r="P52" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
@@ -3663,11 +3576,7 @@
       <c r="O53" t="n">
         <v>48</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
@@ -3729,11 +3638,7 @@
       <c r="O54" t="n">
         <v>55</v>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
     </row>
@@ -3790,9 +3695,6 @@
       </c>
       <c r="O55" t="n">
         <v>72</v>
-      </c>
-      <c r="P55" t="n">
-        <v>13.7</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3968,9 +3870,6 @@
       <c r="O58" t="n">
         <v>43</v>
       </c>
-      <c r="P58" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
@@ -4091,14 +3990,7 @@
       <c r="O60" t="n">
         <v>54</v>
       </c>
-      <c r="P60" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
     </row>
@@ -4214,9 +4106,6 @@
       <c r="O62" t="n">
         <v>84</v>
       </c>
-      <c r="P62" t="n">
-        <v>24.9</v>
-      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
@@ -4275,14 +4164,7 @@
       <c r="O63" t="n">
         <v>54</v>
       </c>
-      <c r="P63" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
     </row>
@@ -4522,11 +4404,7 @@
       <c r="O67" t="n">
         <v>47</v>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4584,14 +4462,7 @@
       <c r="O68" t="n">
         <v>45</v>
       </c>
-      <c r="P68" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
@@ -4653,14 +4524,7 @@
       <c r="O69" t="n">
         <v>54</v>
       </c>
-      <c r="P69" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
     </row>
@@ -4776,14 +4640,7 @@
       <c r="O71" t="n">
         <v>44</v>
       </c>
-      <c r="P71" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
     </row>
@@ -5073,14 +4930,7 @@
       <c r="O76" t="n">
         <v>54</v>
       </c>
-      <c r="P76" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
     </row>
@@ -5138,14 +4988,7 @@
       <c r="O77" t="n">
         <v>47</v>
       </c>
-      <c r="P77" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>Kiwi Strawberry (Pink)</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5203,11 +5046,7 @@
       <c r="O78" t="n">
         <v>48</v>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
     </row>
@@ -5265,11 +5104,7 @@
       <c r="O79" t="n">
         <v>47</v>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5385,14 +5220,7 @@
       <c r="O81" t="n">
         <v>54</v>
       </c>
-      <c r="P81" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
@@ -5512,14 +5340,7 @@
       <c r="O83" t="n">
         <v>30</v>
       </c>
-      <c r="P83" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
@@ -5766,9 +5587,6 @@
       </c>
       <c r="O87" t="n">
         <v>61</v>
-      </c>
-      <c r="P87" t="n">
-        <v>13</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6257,14 +6075,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -6325,9 +6136,6 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -6391,9 +6199,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6580,9 +6385,6 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6645,14 +6447,7 @@
       <c r="O9" t="n">
         <v>39</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
@@ -6713,9 +6508,6 @@
       </c>
       <c r="O10" t="n">
         <v>43</v>
-      </c>
-      <c r="P10" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -6779,14 +6571,7 @@
       <c r="O11" t="n">
         <v>47</v>
       </c>
-      <c r="P11" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6848,14 +6633,7 @@
       <c r="O12" t="n">
         <v>51</v>
       </c>
-      <c r="P12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
@@ -6979,11 +6757,7 @@
       <c r="O14" t="n">
         <v>48</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
@@ -7044,9 +6818,6 @@
       </c>
       <c r="O15" t="n">
         <v>43</v>
-      </c>
-      <c r="P15" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7234,14 +7005,7 @@
       <c r="O18" t="n">
         <v>45</v>
       </c>
-      <c r="P18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
@@ -7303,14 +7067,7 @@
       <c r="O19" t="n">
         <v>54</v>
       </c>
-      <c r="P19" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
@@ -7372,14 +7129,7 @@
       <c r="O20" t="n">
         <v>30</v>
       </c>
-      <c r="P20" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
@@ -7568,9 +7318,6 @@
       </c>
       <c r="O23" t="n">
         <v>61</v>
-      </c>
-      <c r="P23" t="n">
-        <v>13</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -8491,11 +8238,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8551,11 +8294,7 @@
       <c r="O12" t="n">
         <v>48</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8723,14 +8462,7 @@
       <c r="O15" t="n">
         <v>54</v>
       </c>
-      <c r="P15" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9010,11 +8742,7 @@
       <c r="O20" t="n">
         <v>47</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/THC Recommended Order.xlsx
+++ b/data/THC Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,9 +1092,6 @@
       <c r="O11" t="n">
         <v>55</v>
       </c>
-      <c r="P11" t="n">
-        <v>22</v>
-      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
@@ -1211,9 +1208,6 @@
       <c r="O13" t="n">
         <v>55</v>
       </c>
-      <c r="P13" t="n">
-        <v>22</v>
-      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
@@ -1504,9 +1498,6 @@
       <c r="O18" t="n">
         <v>55</v>
       </c>
-      <c r="P18" t="n">
-        <v>22</v>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -1859,14 +1850,7 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="P24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
@@ -1986,11 +1970,7 @@
       <c r="O26" t="n">
         <v>53</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
     </row>
@@ -2047,9 +2027,6 @@
       </c>
       <c r="O27" t="n">
         <v>60</v>
-      </c>
-      <c r="P27" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -2113,9 +2090,6 @@
       <c r="O28" t="n">
         <v>60</v>
       </c>
-      <c r="P28" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
@@ -2236,14 +2210,7 @@
       <c r="O30" t="n">
         <v>54</v>
       </c>
-      <c r="P30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
     </row>
@@ -2300,9 +2267,6 @@
       </c>
       <c r="O31" t="n">
         <v>37</v>
-      </c>
-      <c r="P31" t="n">
-        <v>20</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2362,14 +2326,7 @@
       <c r="O32" t="n">
         <v>39</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
@@ -2493,9 +2450,6 @@
       <c r="O34" t="n">
         <v>87</v>
       </c>
-      <c r="P34" t="n">
-        <v>24.9</v>
-      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
@@ -2554,9 +2508,6 @@
       <c r="O35" t="n">
         <v>60</v>
       </c>
-      <c r="P35" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
@@ -2677,9 +2628,6 @@
       <c r="O37" t="n">
         <v>45</v>
       </c>
-      <c r="P37" t="n">
-        <v>17</v>
-      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
@@ -2738,9 +2686,6 @@
       <c r="O38" t="n">
         <v>43</v>
       </c>
-      <c r="P38" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -2803,14 +2748,7 @@
       <c r="O39" t="n">
         <v>47</v>
       </c>
-      <c r="P39" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
@@ -2930,11 +2868,7 @@
       <c r="O41" t="n">
         <v>48</v>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
     </row>
@@ -3050,14 +2984,7 @@
       <c r="O43" t="n">
         <v>54</v>
       </c>
-      <c r="P43" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
     </row>
@@ -3115,14 +3042,7 @@
       <c r="O44" t="n">
         <v>51</v>
       </c>
-      <c r="P44" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
@@ -3183,9 +3103,6 @@
       </c>
       <c r="O45" t="n">
         <v>60</v>
-      </c>
-      <c r="P45" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3245,9 +3162,6 @@
       <c r="O46" t="n">
         <v>74</v>
       </c>
-      <c r="P46" t="n">
-        <v>13.7</v>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -3306,14 +3220,7 @@
       <c r="O47" t="n">
         <v>54</v>
       </c>
-      <c r="P47" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
     </row>
@@ -3669,11 +3576,7 @@
       <c r="O53" t="n">
         <v>47</v>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
     </row>
@@ -3730,9 +3633,6 @@
       </c>
       <c r="O54" t="n">
         <v>43</v>
-      </c>
-      <c r="P54" t="n">
-        <v>21.1</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -3796,11 +3696,7 @@
       <c r="O55" t="n">
         <v>55</v>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Direct Ship to Blaine</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
     </row>
@@ -3858,14 +3754,7 @@
       <c r="O56" t="n">
         <v>54</v>
       </c>
-      <c r="P56" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
     </row>
@@ -3923,11 +3812,7 @@
       <c r="O57" t="n">
         <v>48</v>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
@@ -4283,14 +4168,7 @@
       <c r="O63" t="n">
         <v>45</v>
       </c>
-      <c r="P63" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
@@ -4526,14 +4404,7 @@
       <c r="O67" t="n">
         <v>44</v>
       </c>
-      <c r="P67" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Blackberry Lemon (Purple)</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
     </row>
@@ -4823,14 +4694,7 @@
       <c r="O72" t="n">
         <v>54</v>
       </c>
-      <c r="P72" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
     </row>
@@ -4888,14 +4752,7 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="P73" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
     </row>
@@ -5015,11 +4872,7 @@
       <c r="O75" t="n">
         <v>48</v>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
     </row>
@@ -5135,14 +4988,7 @@
       <c r="O77" t="n">
         <v>54</v>
       </c>
-      <c r="P77" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
     </row>
@@ -5257,9 +5103,6 @@
       </c>
       <c r="O79" t="n">
         <v>43</v>
-      </c>
-      <c r="P79" t="n">
-        <v>22</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -5860,14 +5703,7 @@
       <c r="O3" t="n">
         <v>45</v>
       </c>
-      <c r="P3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -5928,9 +5764,6 @@
       </c>
       <c r="O4" t="n">
         <v>60</v>
-      </c>
-      <c r="P4" t="n">
-        <v>23.1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -5994,9 +5827,6 @@
       <c r="O5" t="n">
         <v>60</v>
       </c>
-      <c r="P5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -6059,14 +5889,7 @@
       <c r="O6" t="n">
         <v>39</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Pallet Orders</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
@@ -6190,9 +6013,6 @@
       <c r="O8" t="n">
         <v>60</v>
       </c>
-      <c r="P8" t="n">
-        <v>23.1</v>
-      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -6255,9 +6075,6 @@
       <c r="O9" t="n">
         <v>43</v>
       </c>
-      <c r="P9" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
@@ -6320,14 +6137,7 @@
       <c r="O10" t="n">
         <v>47</v>
       </c>
-      <c r="P10" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>15c</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
@@ -6389,14 +6199,7 @@
       <c r="O11" t="n">
         <v>51</v>
       </c>
-      <c r="P11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Extra on 12pk to make up for 4pk</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
@@ -6582,9 +6385,6 @@
       <c r="O14" t="n">
         <v>43</v>
       </c>
-      <c r="P14" t="n">
-        <v>21.1</v>
-      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -6647,11 +6447,7 @@
       <c r="O15" t="n">
         <v>48</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
@@ -6775,14 +6571,7 @@
       <c r="O17" t="n">
         <v>45</v>
       </c>
-      <c r="P17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
@@ -6905,9 +6694,6 @@
       </c>
       <c r="O19" t="n">
         <v>43</v>
-      </c>
-      <c r="P19" t="n">
-        <v>22</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7824,11 +7610,7 @@
       <c r="O11" t="n">
         <v>48</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Quarterly buy</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7996,14 +7778,7 @@
       <c r="O14" t="n">
         <v>54</v>
       </c>
-      <c r="P14" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>$200 order qty per store</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8283,11 +8058,7 @@
       <c r="O19" t="n">
         <v>47</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Case 1 Upfront</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
